--- a/jogos_2025-07-18.xlsx
+++ b/jogos_2025-07-18.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="113">
   <si>
     <t>Date</t>
   </si>
@@ -142,6 +142,9 @@
     <t>08:00</t>
   </si>
   <si>
+    <t>08:30</t>
+  </si>
+  <si>
     <t>08:35</t>
   </si>
   <si>
@@ -181,12 +184,15 @@
     <t>South Korea K League 1</t>
   </si>
   <si>
+    <t>China China League One</t>
+  </si>
+  <si>
+    <t>Finland Veikkausliiga</t>
+  </si>
+  <si>
     <t>Kazakhstan Kazakhstan Premier League</t>
   </si>
   <si>
-    <t>Finland Veikkausliiga</t>
-  </si>
-  <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
@@ -196,15 +202,15 @@
     <t>Argentina Primera División</t>
   </si>
   <si>
+    <t>USA USL Championship</t>
+  </si>
+  <si>
     <t>Canada Canadian Premier League</t>
   </si>
   <si>
     <t>Chile Primera División</t>
   </si>
   <si>
-    <t>USA USL Championship</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
@@ -217,27 +223,30 @@
     <t>Sydney II</t>
   </si>
   <si>
+    <t>Suwon</t>
+  </si>
+  <si>
     <t>Daegu</t>
   </si>
   <si>
-    <t>Suwon</t>
-  </si>
-  <si>
     <t>Wuhan Three Towns</t>
   </si>
   <si>
+    <t>Guangzhou E-Power</t>
+  </si>
+  <si>
     <t>Tianjin Teda</t>
   </si>
   <si>
     <t>Zhejiang FC</t>
   </si>
   <si>
+    <t>KTP</t>
+  </si>
+  <si>
     <t>Astana</t>
   </si>
   <si>
-    <t>KTP</t>
-  </si>
-  <si>
     <t>Sarpsborg 08</t>
   </si>
   <si>
@@ -247,60 +256,63 @@
     <t>Boca Juniors</t>
   </si>
   <si>
+    <t>Detroit City FC</t>
+  </si>
+  <si>
     <t>Atlético Ottawa</t>
   </si>
   <si>
+    <t>Forge FC</t>
+  </si>
+  <si>
     <t>Everton</t>
   </si>
   <si>
-    <t>Forge FC</t>
-  </si>
-  <si>
-    <t>Detroit City FC</t>
-  </si>
-  <si>
     <t>North Carolina FC</t>
   </si>
   <si>
     <t>Huntsville City</t>
   </si>
   <si>
+    <t>Atlético Tucumán</t>
+  </si>
+  <si>
     <t>Ferroviária</t>
   </si>
   <si>
     <t>Sporting KC II</t>
   </si>
   <si>
-    <t>Atlético Tucumán</t>
-  </si>
-  <si>
     <t>Shanghai SIPG</t>
   </si>
   <si>
     <t>Western Sydney W. II</t>
   </si>
   <si>
+    <t>Gwangju</t>
+  </si>
+  <si>
     <t>Sangju Sangmu</t>
   </si>
   <si>
-    <t>Gwangju</t>
-  </si>
-  <si>
     <t>Qingdao Youth Island</t>
   </si>
   <si>
+    <t>Dalian Huayi</t>
+  </si>
+  <si>
     <t>Chengdu Better City FC</t>
   </si>
   <si>
     <t>Yunnan Yukun</t>
   </si>
   <si>
+    <t>Inter Turku</t>
+  </si>
+  <si>
     <t>Turan Turkistan</t>
   </si>
   <si>
-    <t>Inter Turku</t>
-  </si>
-  <si>
     <t>Rosenborg</t>
   </si>
   <si>
@@ -310,31 +322,31 @@
     <t>Unión Santa Fe</t>
   </si>
   <si>
+    <t>Pittsburgh Riverhounds</t>
+  </si>
+  <si>
     <t>HFX Wanderers FC</t>
   </si>
   <si>
+    <t>Pacific FC</t>
+  </si>
+  <si>
     <t>Deportes Limache</t>
   </si>
   <si>
-    <t>Pacific FC</t>
-  </si>
-  <si>
-    <t>Pittsburgh Riverhounds</t>
-  </si>
-  <si>
     <t>Indy Eleven</t>
   </si>
   <si>
     <t>Columbus Crew II</t>
   </si>
   <si>
+    <t>Central Córdoba SdE</t>
+  </si>
+  <si>
     <t>Athletic Club</t>
   </si>
   <si>
     <t>North Texas</t>
-  </si>
-  <si>
-    <t>Central Córdoba SdE</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -704,7 +716,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL22"/>
+  <dimension ref="A1:AL23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:38">
@@ -831,16 +843,16 @@
         <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -855,7 +867,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L2">
         <v>5.6</v>
@@ -930,10 +942,10 @@
         <v>1.36</v>
       </c>
       <c r="AJ2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AK2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AL2" s="3">
         <v>45856.22916666666</v>
@@ -947,16 +959,16 @@
         <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -971,34 +983,34 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L3">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="M3">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="N3">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>20.5</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R3">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S3">
         <v>3.6</v>
       </c>
       <c r="T3">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="U3">
         <v>1.6</v>
@@ -1016,7 +1028,7 @@
         <v>12</v>
       </c>
       <c r="Z3">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AA3">
         <v>4.5</v>
@@ -1025,31 +1037,31 @@
         <v>1.57</v>
       </c>
       <c r="AC3">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AD3">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="AE3">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AF3">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG3">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AH3">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AI3">
         <v>1.2</v>
       </c>
       <c r="AJ3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AK3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AL3" s="3">
         <v>45856.27083333334</v>
@@ -1063,16 +1075,16 @@
         <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1087,85 +1099,85 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L4">
-        <v>3.47</v>
+        <v>2.67</v>
       </c>
       <c r="M4">
-        <v>3.45</v>
+        <v>3.03</v>
       </c>
       <c r="N4">
-        <v>1.85</v>
+        <v>2.41</v>
       </c>
       <c r="O4">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="P4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q4">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="R4">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S4">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="T4">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="U4">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="V4">
-        <v>5.65</v>
+        <v>7</v>
       </c>
       <c r="W4">
         <v>1.08</v>
       </c>
       <c r="X4">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z4">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AA4">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="AB4">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AC4">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AD4">
-        <v>2.6</v>
+        <v>3.45</v>
       </c>
       <c r="AE4">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AF4">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AG4">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AH4">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="AI4">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AJ4" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AK4" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AL4" s="3">
         <v>45856.3125</v>
@@ -1179,16 +1191,16 @@
         <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1203,85 +1215,85 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L5">
-        <v>2.67</v>
+        <v>3.47</v>
       </c>
       <c r="M5">
-        <v>3.03</v>
+        <v>3.45</v>
       </c>
       <c r="N5">
-        <v>2.41</v>
+        <v>1.85</v>
       </c>
       <c r="O5">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="P5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="R5">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S5">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="T5">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="U5">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="V5">
-        <v>7</v>
+        <v>5.65</v>
       </c>
       <c r="W5">
         <v>1.08</v>
       </c>
       <c r="X5">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z5">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AA5">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="AB5">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AC5">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AD5">
-        <v>3.45</v>
+        <v>2.6</v>
       </c>
       <c r="AE5">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AF5">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AG5">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH5">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="AI5">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AJ5" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AK5" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AL5" s="3">
         <v>45856.3125</v>
@@ -1295,16 +1307,16 @@
         <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1319,7 +1331,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L6">
         <v>2.09</v>
@@ -1394,10 +1406,10 @@
         <v>1.11</v>
       </c>
       <c r="AJ6" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AK6" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AL6" s="3">
         <v>45856.33333333334</v>
@@ -1411,16 +1423,16 @@
         <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1435,88 +1447,88 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L7">
-        <v>5.55</v>
+        <v>1.6</v>
       </c>
       <c r="M7">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="N7">
-        <v>1.52</v>
+        <v>4.6</v>
       </c>
       <c r="O7">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>17.75</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="R7">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S7">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V7">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="W7">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z7">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AC7">
-        <v>2.35</v>
+        <v>1.91</v>
       </c>
       <c r="AD7">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AE7">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF7">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG7">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH7">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AI7">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AK7" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AL7" s="3">
-        <v>45856.35763888889</v>
+        <v>45856.35416666666</v>
       </c>
     </row>
     <row r="8" spans="1:38">
@@ -1527,16 +1539,16 @@
         <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F8" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1551,88 +1563,88 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L8">
-        <v>1.82</v>
+        <v>5.55</v>
       </c>
       <c r="M8">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="N8">
-        <v>3.85</v>
+        <v>1.52</v>
       </c>
       <c r="O8">
-        <v>1.63</v>
+        <v>2.94</v>
       </c>
       <c r="P8">
-        <v>19.25</v>
+        <v>17.75</v>
       </c>
       <c r="Q8">
-        <v>2.28</v>
+        <v>1.42</v>
       </c>
       <c r="R8">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="S8">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="T8">
-        <v>2.14</v>
+        <v>2.31</v>
       </c>
       <c r="U8">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="V8">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="W8">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Z8">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AA8">
-        <v>5.7</v>
+        <v>4.65</v>
       </c>
       <c r="AB8">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AC8">
-        <v>2.57</v>
+        <v>2.35</v>
       </c>
       <c r="AD8">
-        <v>2.16</v>
+        <v>2.33</v>
       </c>
       <c r="AE8">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AF8">
-        <v>1.42</v>
+        <v>1.64</v>
       </c>
       <c r="AG8">
-        <v>2.65</v>
+        <v>2.12</v>
       </c>
       <c r="AH8">
-        <v>3.52</v>
+        <v>4.15</v>
       </c>
       <c r="AI8">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AJ8" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AK8" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AL8" s="3">
-        <v>45856.375</v>
+        <v>45856.35763888889</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -1643,16 +1655,16 @@
         <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F9" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1667,88 +1679,88 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L9">
-        <v>1.11</v>
+        <v>1.82</v>
       </c>
       <c r="M9">
-        <v>8.65</v>
+        <v>3.8</v>
       </c>
       <c r="N9">
-        <v>20</v>
+        <v>3.85</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>19.25</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R9">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="S9">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="T9">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="U9">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="V9">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="W9">
         <v>1.13</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z9">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AA9">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="AB9">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AC9">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AD9">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="AE9">
-        <v>1.51</v>
+        <v>1.7</v>
       </c>
       <c r="AF9">
-        <v>3.9</v>
+        <v>1.42</v>
       </c>
       <c r="AG9">
-        <v>1.24</v>
+        <v>2.65</v>
       </c>
       <c r="AH9">
-        <v>4.3</v>
+        <v>3.52</v>
       </c>
       <c r="AI9">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AJ9" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AK9" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AL9" s="3">
-        <v>45856.5</v>
+        <v>45856.375</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -1756,19 +1768,19 @@
         <v>45856</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1783,7 +1795,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L10">
         <v>5.4</v>
@@ -1804,25 +1816,25 @@
         <v>1.3</v>
       </c>
       <c r="R10">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S10">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="T10">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="U10">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="V10">
-        <v>4.65</v>
+        <v>4.4</v>
       </c>
       <c r="W10">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X10">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
         <v>12</v>
@@ -1849,19 +1861,19 @@
         <v>1.7</v>
       </c>
       <c r="AG10">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AH10">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="AI10">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AJ10" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AK10" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AL10" s="3">
         <v>45856.5</v>
@@ -1875,16 +1887,16 @@
         <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E11" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F11" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1899,88 +1911,88 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L11">
-        <v>2.45</v>
+        <v>1.06</v>
       </c>
       <c r="M11">
-        <v>3.34</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N11">
-        <v>2.43</v>
+        <v>23</v>
       </c>
       <c r="O11">
-        <v>1.95</v>
+        <v>1.04</v>
       </c>
       <c r="P11">
+        <v>17</v>
+      </c>
+      <c r="Q11">
         <v>10</v>
       </c>
-      <c r="Q11">
-        <v>2</v>
-      </c>
       <c r="R11">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S11">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T11">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="U11">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="V11">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="W11">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="Z11">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AA11">
-        <v>4.33</v>
+        <v>4.35</v>
       </c>
       <c r="AB11">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AC11">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="AD11">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AE11">
         <v>1.5</v>
       </c>
       <c r="AF11">
-        <v>1.48</v>
+        <v>4.1</v>
       </c>
       <c r="AG11">
-        <v>2.4</v>
+        <v>1.22</v>
       </c>
       <c r="AH11">
         <v>4.33</v>
       </c>
       <c r="AI11">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AJ11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AK11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AL11" s="3">
-        <v>45856.54166666666</v>
+        <v>45856.5</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -1991,16 +2003,16 @@
         <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2015,88 +2027,88 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L12">
-        <v>1.76</v>
+        <v>2.45</v>
       </c>
       <c r="M12">
-        <v>3.06</v>
+        <v>3.34</v>
       </c>
       <c r="N12">
-        <v>4.4</v>
+        <v>2.43</v>
       </c>
       <c r="O12">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="P12">
-        <v>6.5</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>2.95</v>
+        <v>2</v>
       </c>
       <c r="R12">
+        <v>1.3</v>
+      </c>
+      <c r="S12">
+        <v>3.2</v>
+      </c>
+      <c r="T12">
+        <v>2.3</v>
+      </c>
+      <c r="U12">
+        <v>1.55</v>
+      </c>
+      <c r="V12">
+        <v>5.5</v>
+      </c>
+      <c r="W12">
+        <v>1.08</v>
+      </c>
+      <c r="X12">
+        <v>1.04</v>
+      </c>
+      <c r="Y12">
+        <v>10</v>
+      </c>
+      <c r="Z12">
+        <v>1.2</v>
+      </c>
+      <c r="AA12">
+        <v>4.33</v>
+      </c>
+      <c r="AB12">
+        <v>1.55</v>
+      </c>
+      <c r="AC12">
+        <v>2.2</v>
+      </c>
+      <c r="AD12">
+        <v>2.55</v>
+      </c>
+      <c r="AE12">
         <v>1.5</v>
       </c>
-      <c r="S12">
+      <c r="AF12">
+        <v>1.48</v>
+      </c>
+      <c r="AG12">
         <v>2.4</v>
       </c>
-      <c r="T12">
-        <v>3.3</v>
-      </c>
-      <c r="U12">
-        <v>1.29</v>
-      </c>
-      <c r="V12">
-        <v>9</v>
-      </c>
-      <c r="W12">
-        <v>1.03</v>
-      </c>
-      <c r="X12">
-        <v>1.09</v>
-      </c>
-      <c r="Y12">
-        <v>7</v>
-      </c>
-      <c r="Z12">
-        <v>1.44</v>
-      </c>
-      <c r="AA12">
-        <v>2.44</v>
-      </c>
-      <c r="AB12">
-        <v>2.15</v>
-      </c>
-      <c r="AC12">
-        <v>1.57</v>
-      </c>
-      <c r="AD12">
-        <v>5</v>
-      </c>
-      <c r="AE12">
-        <v>1.17</v>
-      </c>
-      <c r="AF12">
-        <v>2.25</v>
-      </c>
-      <c r="AG12">
-        <v>1.57</v>
-      </c>
       <c r="AH12">
-        <v>9.5</v>
+        <v>4.33</v>
       </c>
       <c r="AI12">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="AJ12" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AK12" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AL12" s="3">
-        <v>45856.79166666666</v>
+        <v>45856.54166666666</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -2107,16 +2119,16 @@
         <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E13" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F13" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2131,88 +2143,88 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L13">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="M13">
-        <v>3.95</v>
+        <v>3.06</v>
       </c>
       <c r="N13">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="O13">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="P13">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q13">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="R13">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="S13">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="T13">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="U13">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="V13">
-        <v>7.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W13">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="X13">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Y13">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="Z13">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AA13">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="AB13">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC13">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AD13">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AE13">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AF13">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AG13">
         <v>1.57</v>
       </c>
       <c r="AH13">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="AI13">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AJ13" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AK13" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AL13" s="3">
-        <v>45856.8125</v>
+        <v>45856.79166666666</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -2223,16 +2235,16 @@
         <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E14" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F14" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2247,88 +2259,88 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L14">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="M14">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="N14">
-        <v>3.7</v>
+        <v>6.2</v>
       </c>
       <c r="O14">
+        <v>1.45</v>
+      </c>
+      <c r="P14">
+        <v>8.5</v>
+      </c>
+      <c r="Q14">
+        <v>3.4</v>
+      </c>
+      <c r="R14">
+        <v>1.42</v>
+      </c>
+      <c r="S14">
+        <v>2.62</v>
+      </c>
+      <c r="T14">
+        <v>3</v>
+      </c>
+      <c r="U14">
+        <v>1.33</v>
+      </c>
+      <c r="V14">
+        <v>7.5</v>
+      </c>
+      <c r="W14">
+        <v>1.06</v>
+      </c>
+      <c r="X14">
+        <v>1.06</v>
+      </c>
+      <c r="Y14">
+        <v>8.5</v>
+      </c>
+      <c r="Z14">
+        <v>1.38</v>
+      </c>
+      <c r="AA14">
+        <v>3</v>
+      </c>
+      <c r="AB14">
+        <v>2.2</v>
+      </c>
+      <c r="AC14">
+        <v>1.65</v>
+      </c>
+      <c r="AD14">
+        <v>4.2</v>
+      </c>
+      <c r="AE14">
+        <v>1.22</v>
+      </c>
+      <c r="AF14">
+        <v>2.25</v>
+      </c>
+      <c r="AG14">
         <v>1.57</v>
       </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>2.6</v>
-      </c>
-      <c r="R14">
-        <v>1.36</v>
-      </c>
-      <c r="S14">
-        <v>3</v>
-      </c>
-      <c r="T14">
-        <v>2.63</v>
-      </c>
-      <c r="U14">
-        <v>1.44</v>
-      </c>
-      <c r="V14">
-        <v>6</v>
-      </c>
-      <c r="W14">
-        <v>1.11</v>
-      </c>
-      <c r="X14">
-        <v>0</v>
-      </c>
-      <c r="Y14">
-        <v>0</v>
-      </c>
-      <c r="Z14">
-        <v>0</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <v>1.8</v>
-      </c>
-      <c r="AC14">
-        <v>2</v>
-      </c>
-      <c r="AD14">
-        <v>0</v>
-      </c>
-      <c r="AE14">
-        <v>0</v>
-      </c>
-      <c r="AF14">
-        <v>1.8</v>
-      </c>
-      <c r="AG14">
-        <v>1.91</v>
-      </c>
       <c r="AH14">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ14" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AK14" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AL14" s="3">
-        <v>45856.83333333334</v>
+        <v>45856.8125</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2336,19 +2348,19 @@
         <v>45856</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F15" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2363,85 +2375,85 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L15">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="M15">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="N15">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O15">
-        <v>1.78</v>
+        <v>1.99</v>
       </c>
       <c r="P15">
+        <v>6.6</v>
+      </c>
+      <c r="Q15">
+        <v>2.16</v>
+      </c>
+      <c r="R15">
+        <v>1.53</v>
+      </c>
+      <c r="S15">
+        <v>2.4</v>
+      </c>
+      <c r="T15">
+        <v>3.65</v>
+      </c>
+      <c r="U15">
+        <v>1.29</v>
+      </c>
+      <c r="V15">
+        <v>9.5</v>
+      </c>
+      <c r="W15">
+        <v>1.05</v>
+      </c>
+      <c r="X15">
+        <v>1.09</v>
+      </c>
+      <c r="Y15">
+        <v>6</v>
+      </c>
+      <c r="Z15">
+        <v>1.49</v>
+      </c>
+      <c r="AA15">
+        <v>2.44</v>
+      </c>
+      <c r="AB15">
+        <v>2.5</v>
+      </c>
+      <c r="AC15">
+        <v>1.5</v>
+      </c>
+      <c r="AD15">
+        <v>5.2</v>
+      </c>
+      <c r="AE15">
+        <v>1.14</v>
+      </c>
+      <c r="AF15">
+        <v>2.05</v>
+      </c>
+      <c r="AG15">
+        <v>1.65</v>
+      </c>
+      <c r="AH15">
         <v>10</v>
       </c>
-      <c r="Q15">
-        <v>2.2</v>
-      </c>
-      <c r="R15">
-        <v>1.35</v>
-      </c>
-      <c r="S15">
-        <v>2.9</v>
-      </c>
-      <c r="T15">
-        <v>2.6</v>
-      </c>
-      <c r="U15">
-        <v>1.43</v>
-      </c>
-      <c r="V15">
-        <v>6.5</v>
-      </c>
-      <c r="W15">
-        <v>1.1</v>
-      </c>
-      <c r="X15">
-        <v>1.05</v>
-      </c>
-      <c r="Y15">
-        <v>8.5</v>
-      </c>
-      <c r="Z15">
-        <v>1.25</v>
-      </c>
-      <c r="AA15">
-        <v>3.6</v>
-      </c>
-      <c r="AB15">
-        <v>1.77</v>
-      </c>
-      <c r="AC15">
-        <v>1.9</v>
-      </c>
-      <c r="AD15">
-        <v>3</v>
-      </c>
-      <c r="AE15">
-        <v>1.36</v>
-      </c>
-      <c r="AF15">
-        <v>1.68</v>
-      </c>
-      <c r="AG15">
-        <v>2.05</v>
-      </c>
-      <c r="AH15">
-        <v>5.4</v>
-      </c>
       <c r="AI15">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AJ15" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AK15" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AL15" s="3">
         <v>45856.83333333334</v>
@@ -2452,19 +2464,19 @@
         <v>45856</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F16" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2479,25 +2491,25 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L16">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="M16">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="N16">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="O16">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="P16">
         <v>0</v>
       </c>
       <c r="Q16">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="R16">
         <v>1.36</v>
@@ -2506,16 +2518,16 @@
         <v>3</v>
       </c>
       <c r="T16">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U16">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V16">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W16">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
         <v>0</v>
@@ -2530,10 +2542,10 @@
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC16">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AD16">
         <v>0</v>
@@ -2542,10 +2554,10 @@
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AG16">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AH16">
         <v>0</v>
@@ -2554,10 +2566,10 @@
         <v>0</v>
       </c>
       <c r="AJ16" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AK16" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AL16" s="3">
         <v>45856.83333333334</v>
@@ -2568,19 +2580,19 @@
         <v>45856</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E17" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F17" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2595,85 +2607,85 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L17">
-        <v>2.16</v>
+        <v>1.6</v>
       </c>
       <c r="M17">
+        <v>3.65</v>
+      </c>
+      <c r="N17">
+        <v>4.9</v>
+      </c>
+      <c r="O17">
+        <v>1.4</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>3.5</v>
+      </c>
+      <c r="R17">
+        <v>1.36</v>
+      </c>
+      <c r="S17">
         <v>3</v>
       </c>
-      <c r="N17">
-        <v>3.25</v>
-      </c>
-      <c r="O17">
-        <v>1.99</v>
-      </c>
-      <c r="P17">
-        <v>6.6</v>
-      </c>
-      <c r="Q17">
-        <v>2.16</v>
-      </c>
-      <c r="R17">
-        <v>1.53</v>
-      </c>
-      <c r="S17">
-        <v>2.15</v>
-      </c>
       <c r="T17">
-        <v>3.65</v>
+        <v>2.75</v>
       </c>
       <c r="U17">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="V17">
-        <v>9.5</v>
+        <v>6.5</v>
       </c>
       <c r="W17">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X17">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y17">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="AC17">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="AD17">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AE17">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG17">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH17">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AI17">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AK17" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AL17" s="3">
         <v>45856.83333333334</v>
@@ -2687,16 +2699,16 @@
         <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E18" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F18" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2711,88 +2723,88 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L18">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="M18">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N18">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="O18">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="P18">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="R18">
         <v>1.35</v>
       </c>
       <c r="S18">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="T18">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="U18">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="V18">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W18">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X18">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y18">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="Z18">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AA18">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AB18">
+        <v>1.77</v>
+      </c>
+      <c r="AC18">
         <v>1.9</v>
       </c>
-      <c r="AC18">
-        <v>1.81</v>
-      </c>
       <c r="AD18">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="AE18">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AF18">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AG18">
         <v>2.05</v>
       </c>
       <c r="AH18">
-        <v>6.55</v>
+        <v>5.4</v>
       </c>
       <c r="AI18">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AJ18" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AK18" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AL18" s="3">
-        <v>45856.85416666666</v>
+        <v>45856.83333333334</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -2803,16 +2815,16 @@
         <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D19" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E19" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F19" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2827,88 +2839,88 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ19" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AK19" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AL19" s="3">
-        <v>45856.875</v>
+        <v>45856.85416666666</v>
       </c>
     </row>
     <row r="20" spans="1:38">
@@ -2919,16 +2931,16 @@
         <v>51</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D20" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E20" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F20" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2943,88 +2955,88 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L20">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M20">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N20">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="O20">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P20">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="Q20">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R20">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S20">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T20">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U20">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V20">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W20">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X20">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y20">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="Z20">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA20">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB20">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC20">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD20">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AE20">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF20">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG20">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH20">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AI20">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AK20" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AL20" s="3">
-        <v>45856.89583333334</v>
+        <v>45856.875</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -3032,19 +3044,19 @@
         <v>45856</v>
       </c>
       <c r="B21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C21" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D21" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E21" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F21" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3059,85 +3071,85 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI21">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ21" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AK21" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AL21" s="3">
         <v>45856.89583333334</v>
@@ -3148,19 +3160,19 @@
         <v>45856</v>
       </c>
       <c r="B22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D22" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E22" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F22" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3175,87 +3187,203 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="L22">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="M22">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="N22">
-        <v>3.9</v>
+        <v>3.97</v>
       </c>
       <c r="O22">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="P22">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q22">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="R22">
+        <v>1.55</v>
+      </c>
+      <c r="S22">
+        <v>2.39</v>
+      </c>
+      <c r="T22">
+        <v>3.48</v>
+      </c>
+      <c r="U22">
+        <v>1.26</v>
+      </c>
+      <c r="V22">
+        <v>9.9</v>
+      </c>
+      <c r="W22">
+        <v>1</v>
+      </c>
+      <c r="X22">
+        <v>1.05</v>
+      </c>
+      <c r="Y22">
+        <v>8</v>
+      </c>
+      <c r="Z22">
         <v>1.5</v>
-      </c>
-      <c r="S22">
-        <v>2.5</v>
-      </c>
-      <c r="T22">
-        <v>3.4</v>
-      </c>
-      <c r="U22">
-        <v>1.3</v>
-      </c>
-      <c r="V22">
-        <v>10</v>
-      </c>
-      <c r="W22">
-        <v>1.06</v>
-      </c>
-      <c r="X22">
-        <v>1.1</v>
-      </c>
-      <c r="Y22">
-        <v>6.5</v>
-      </c>
-      <c r="Z22">
-        <v>1.45</v>
       </c>
       <c r="AA22">
         <v>2.7</v>
       </c>
       <c r="AB22">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AC22">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AD22">
-        <v>4.33</v>
+        <v>4.85</v>
       </c>
       <c r="AE22">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF22">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AG22">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH22">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI22">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AJ22" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AK22" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AL22" s="3">
+        <v>45856.89583333334</v>
+      </c>
+    </row>
+    <row r="23" spans="1:38">
+      <c r="A23" s="2">
+        <v>45856</v>
+      </c>
+      <c r="B23" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" t="s">
+        <v>65</v>
+      </c>
+      <c r="D23" t="s">
+        <v>66</v>
+      </c>
+      <c r="E23" t="s">
+        <v>88</v>
+      </c>
+      <c r="F23" t="s">
+        <v>110</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23" t="s">
+        <v>111</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23">
+        <v>0</v>
+      </c>
+      <c r="AI23">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="s">
+        <v>112</v>
+      </c>
+      <c r="AK23" t="s">
+        <v>112</v>
+      </c>
+      <c r="AL23" s="3">
         <v>45856.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-07-18.xlsx
+++ b/jogos_2025-07-18.xlsx
@@ -187,12 +187,12 @@
     <t>China China League One</t>
   </si>
   <si>
+    <t>Kazakhstan Kazakhstan Premier League</t>
+  </si>
+  <si>
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
-    <t>Kazakhstan Kazakhstan Premier League</t>
-  </si>
-  <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
@@ -223,12 +223,12 @@
     <t>Sydney II</t>
   </si>
   <si>
+    <t>Daegu</t>
+  </si>
+  <si>
     <t>Suwon</t>
   </si>
   <si>
-    <t>Daegu</t>
-  </si>
-  <si>
     <t>Wuhan Three Towns</t>
   </si>
   <si>
@@ -241,12 +241,12 @@
     <t>Zhejiang FC</t>
   </si>
   <si>
+    <t>Astana</t>
+  </si>
+  <si>
     <t>KTP</t>
   </si>
   <si>
-    <t>Astana</t>
-  </si>
-  <si>
     <t>Sarpsborg 08</t>
   </si>
   <si>
@@ -274,27 +274,27 @@
     <t>Huntsville City</t>
   </si>
   <si>
+    <t>Ferroviária</t>
+  </si>
+  <si>
+    <t>Sporting KC II</t>
+  </si>
+  <si>
     <t>Atlético Tucumán</t>
   </si>
   <si>
-    <t>Ferroviária</t>
-  </si>
-  <si>
-    <t>Sporting KC II</t>
-  </si>
-  <si>
     <t>Shanghai SIPG</t>
   </si>
   <si>
     <t>Western Sydney W. II</t>
   </si>
   <si>
+    <t>Sangju Sangmu</t>
+  </si>
+  <si>
     <t>Gwangju</t>
   </si>
   <si>
-    <t>Sangju Sangmu</t>
-  </si>
-  <si>
     <t>Qingdao Youth Island</t>
   </si>
   <si>
@@ -307,12 +307,12 @@
     <t>Yunnan Yukun</t>
   </si>
   <si>
+    <t>Turan Turkistan</t>
+  </si>
+  <si>
     <t>Inter Turku</t>
   </si>
   <si>
-    <t>Turan Turkistan</t>
-  </si>
-  <si>
     <t>Rosenborg</t>
   </si>
   <si>
@@ -340,13 +340,13 @@
     <t>Columbus Crew II</t>
   </si>
   <si>
+    <t>Athletic Club</t>
+  </si>
+  <si>
+    <t>North Texas</t>
+  </si>
+  <si>
     <t>Central Córdoba SdE</t>
-  </si>
-  <si>
-    <t>Athletic Club</t>
-  </si>
-  <si>
-    <t>North Texas</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -924,10 +924,10 @@
         <v>3.08</v>
       </c>
       <c r="AD2">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AE2">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="AF2">
         <v>1.51</v>
@@ -986,13 +986,13 @@
         <v>111</v>
       </c>
       <c r="L3">
-        <v>1.99</v>
+        <v>1.67</v>
       </c>
       <c r="M3">
-        <v>3.85</v>
+        <v>4.01</v>
       </c>
       <c r="N3">
-        <v>2.9</v>
+        <v>3.77</v>
       </c>
       <c r="O3">
         <v>1.68</v>
@@ -1004,22 +1004,22 @@
         <v>2.12</v>
       </c>
       <c r="R3">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="S3">
+        <v>4.5</v>
+      </c>
+      <c r="T3">
+        <v>1.89</v>
+      </c>
+      <c r="U3">
+        <v>1.91</v>
+      </c>
+      <c r="V3">
         <v>3.6</v>
       </c>
-      <c r="T3">
-        <v>2.3</v>
-      </c>
-      <c r="U3">
-        <v>1.6</v>
-      </c>
-      <c r="V3">
-        <v>4.75</v>
-      </c>
       <c r="W3">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="X3">
         <v>1</v>
@@ -1028,34 +1028,34 @@
         <v>12</v>
       </c>
       <c r="Z3">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AA3">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="AB3">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AC3">
-        <v>2.35</v>
+        <v>3.14</v>
       </c>
       <c r="AD3">
-        <v>2.41</v>
+        <v>1.81</v>
       </c>
       <c r="AE3">
-        <v>1.45</v>
+        <v>1.93</v>
       </c>
       <c r="AF3">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="AG3">
-        <v>2.38</v>
+        <v>2.9</v>
       </c>
       <c r="AH3">
-        <v>4.3</v>
+        <v>2.74</v>
       </c>
       <c r="AI3">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AJ3" t="s">
         <v>112</v>
@@ -1102,76 +1102,76 @@
         <v>111</v>
       </c>
       <c r="L4">
-        <v>2.67</v>
+        <v>3.47</v>
       </c>
       <c r="M4">
-        <v>3.03</v>
+        <v>3.45</v>
       </c>
       <c r="N4">
-        <v>2.41</v>
+        <v>1.85</v>
       </c>
       <c r="O4">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="P4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="R4">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S4">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="T4">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="U4">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="V4">
-        <v>7</v>
+        <v>5.65</v>
       </c>
       <c r="W4">
         <v>1.08</v>
       </c>
       <c r="X4">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z4">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AA4">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="AB4">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AC4">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AD4">
-        <v>3.45</v>
+        <v>2.6</v>
       </c>
       <c r="AE4">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AF4">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AG4">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH4">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="AI4">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AJ4" t="s">
         <v>112</v>
@@ -1218,76 +1218,76 @@
         <v>111</v>
       </c>
       <c r="L5">
-        <v>3.47</v>
+        <v>2.67</v>
       </c>
       <c r="M5">
-        <v>3.45</v>
+        <v>3.03</v>
       </c>
       <c r="N5">
-        <v>1.85</v>
+        <v>2.41</v>
       </c>
       <c r="O5">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="P5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q5">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="R5">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S5">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="T5">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="U5">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="V5">
-        <v>5.65</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>1.08</v>
       </c>
       <c r="X5">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z5">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AA5">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="AB5">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AC5">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AD5">
-        <v>2.6</v>
+        <v>3.45</v>
       </c>
       <c r="AE5">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AF5">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AG5">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AH5">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="AI5">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AJ5" t="s">
         <v>112</v>
@@ -1382,10 +1382,10 @@
         <v>4.25</v>
       </c>
       <c r="AB6">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC6">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AD6">
         <v>2.6</v>
@@ -1450,76 +1450,76 @@
         <v>111</v>
       </c>
       <c r="L7">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="M7">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N7">
-        <v>4.6</v>
+        <v>4.11</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AB7">
+        <v>1.93</v>
+      </c>
+      <c r="AC7">
         <v>1.77</v>
       </c>
-      <c r="AC7">
-        <v>1.91</v>
-      </c>
       <c r="AD7">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ7" t="s">
         <v>112</v>
@@ -1736,10 +1736,10 @@
         <v>2.25</v>
       </c>
       <c r="AD9">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AE9">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AF9">
         <v>1.42</v>
@@ -1798,76 +1798,76 @@
         <v>111</v>
       </c>
       <c r="L10">
-        <v>5.4</v>
+        <v>1.06</v>
       </c>
       <c r="M10">
-        <v>3.76</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N10">
-        <v>1.49</v>
+        <v>23</v>
       </c>
       <c r="O10">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="P10">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Q10">
-        <v>1.3</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="S10">
-        <v>3.34</v>
+        <v>3.48</v>
       </c>
       <c r="T10">
-        <v>2.02</v>
+        <v>2.34</v>
       </c>
       <c r="U10">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="V10">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="W10">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y10">
         <v>12</v>
       </c>
       <c r="Z10">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AA10">
-        <v>5</v>
+        <v>4.35</v>
       </c>
       <c r="AB10">
         <v>1.57</v>
       </c>
       <c r="AC10">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AD10">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AE10">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AF10">
-        <v>1.7</v>
+        <v>4.65</v>
       </c>
       <c r="AG10">
-        <v>2.1</v>
+        <v>1.18</v>
       </c>
       <c r="AH10">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AI10">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AJ10" t="s">
         <v>112</v>
@@ -1914,76 +1914,76 @@
         <v>111</v>
       </c>
       <c r="L11">
-        <v>1.06</v>
+        <v>6.5</v>
       </c>
       <c r="M11">
-        <v>8.199999999999999</v>
+        <v>4.84</v>
       </c>
       <c r="N11">
-        <v>23</v>
+        <v>1.36</v>
       </c>
       <c r="O11">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="P11">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Q11">
-        <v>10</v>
+        <v>1.3</v>
       </c>
       <c r="R11">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S11">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="T11">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="U11">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="V11">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="W11">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X11">
         <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z11">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AA11">
-        <v>4.35</v>
+        <v>5.55</v>
       </c>
       <c r="AB11">
+        <v>1.5</v>
+      </c>
+      <c r="AC11">
+        <v>2.5</v>
+      </c>
+      <c r="AD11">
+        <v>2.2</v>
+      </c>
+      <c r="AE11">
         <v>1.6</v>
       </c>
-      <c r="AC11">
-        <v>2.29</v>
-      </c>
-      <c r="AD11">
-        <v>2.4</v>
-      </c>
-      <c r="AE11">
-        <v>1.5</v>
-      </c>
       <c r="AF11">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="AG11">
-        <v>1.22</v>
+        <v>2.1</v>
       </c>
       <c r="AH11">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="AI11">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AJ11" t="s">
         <v>112</v>
@@ -2146,13 +2146,13 @@
         <v>111</v>
       </c>
       <c r="L13">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="M13">
-        <v>3.06</v>
+        <v>3.3</v>
       </c>
       <c r="N13">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="O13">
         <v>1.6</v>
@@ -2164,7 +2164,7 @@
         <v>2.95</v>
       </c>
       <c r="R13">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="S13">
         <v>2.4</v>
@@ -2179,7 +2179,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="W13">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X13">
         <v>1.09</v>
@@ -2191,22 +2191,22 @@
         <v>1.44</v>
       </c>
       <c r="AA13">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AB13">
-        <v>2.15</v>
+        <v>2.56</v>
       </c>
       <c r="AC13">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AD13">
         <v>4.7</v>
       </c>
       <c r="AE13">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF13">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AG13">
         <v>1.57</v>
@@ -2378,13 +2378,13 @@
         <v>111</v>
       </c>
       <c r="L15">
-        <v>2.16</v>
+        <v>2.51</v>
       </c>
       <c r="M15">
         <v>3</v>
       </c>
       <c r="N15">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="O15">
         <v>1.99</v>
@@ -2402,13 +2402,13 @@
         <v>2.4</v>
       </c>
       <c r="T15">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="U15">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V15">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="W15">
         <v>1.05</v>
@@ -2420,31 +2420,31 @@
         <v>6</v>
       </c>
       <c r="Z15">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AA15">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AB15">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AC15">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AD15">
-        <v>5.2</v>
+        <v>4.55</v>
       </c>
       <c r="AE15">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF15">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AG15">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AH15">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="AI15">
         <v>1.04</v>
@@ -2610,13 +2610,13 @@
         <v>111</v>
       </c>
       <c r="L17">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="M17">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="N17">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="O17">
         <v>1.4</v>
@@ -2842,13 +2842,13 @@
         <v>111</v>
       </c>
       <c r="L19">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="M19">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="N19">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O19">
         <v>1.7</v>
@@ -2863,7 +2863,7 @@
         <v>1.38</v>
       </c>
       <c r="S19">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="T19">
         <v>2.8</v>
@@ -2875,13 +2875,13 @@
         <v>6</v>
       </c>
       <c r="W19">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X19">
         <v>1.06</v>
       </c>
       <c r="Y19">
-        <v>9.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z19">
         <v>1.3</v>
@@ -2890,19 +2890,19 @@
         <v>3.3</v>
       </c>
       <c r="AB19">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AC19">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AD19">
         <v>3.4</v>
       </c>
       <c r="AE19">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF19">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AG19">
         <v>1.95</v>
@@ -2911,7 +2911,7 @@
         <v>6.5</v>
       </c>
       <c r="AI19">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AJ19" t="s">
         <v>112</v>
@@ -2958,34 +2958,34 @@
         <v>111</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P20">
         <v>0</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V20">
         <v>0</v>
@@ -3000,34 +3000,34 @@
         <v>0</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH20">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AI20">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ20" t="s">
         <v>112</v>
@@ -3047,7 +3047,7 @@
         <v>52</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D21" t="s">
         <v>66</v>
@@ -3074,76 +3074,76 @@
         <v>111</v>
       </c>
       <c r="L21">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="M21">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="N21">
-        <v>3.9</v>
+        <v>3.14</v>
       </c>
       <c r="O21">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="P21">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q21">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="R21">
+        <v>1.55</v>
+      </c>
+      <c r="S21">
+        <v>2.39</v>
+      </c>
+      <c r="T21">
+        <v>3.5</v>
+      </c>
+      <c r="U21">
+        <v>1.26</v>
+      </c>
+      <c r="V21">
+        <v>9.9</v>
+      </c>
+      <c r="W21">
+        <v>1.04</v>
+      </c>
+      <c r="X21">
+        <v>1.05</v>
+      </c>
+      <c r="Y21">
+        <v>8</v>
+      </c>
+      <c r="Z21">
         <v>1.5</v>
-      </c>
-      <c r="S21">
-        <v>2.5</v>
-      </c>
-      <c r="T21">
-        <v>3.4</v>
-      </c>
-      <c r="U21">
-        <v>1.3</v>
-      </c>
-      <c r="V21">
-        <v>10</v>
-      </c>
-      <c r="W21">
-        <v>1.06</v>
-      </c>
-      <c r="X21">
-        <v>1.1</v>
-      </c>
-      <c r="Y21">
-        <v>6.5</v>
-      </c>
-      <c r="Z21">
-        <v>1.45</v>
       </c>
       <c r="AA21">
         <v>2.7</v>
       </c>
       <c r="AB21">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AC21">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AD21">
-        <v>4.33</v>
+        <v>4.85</v>
       </c>
       <c r="AE21">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF21">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AG21">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH21">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI21">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AJ21" t="s">
         <v>112</v>
@@ -3163,7 +3163,7 @@
         <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D22" t="s">
         <v>66</v>
@@ -3190,76 +3190,76 @@
         <v>111</v>
       </c>
       <c r="L22">
-        <v>1.79</v>
+        <v>5.05</v>
       </c>
       <c r="M22">
-        <v>3.23</v>
+        <v>4.35</v>
       </c>
       <c r="N22">
-        <v>3.97</v>
+        <v>1.49</v>
       </c>
       <c r="O22">
-        <v>1.83</v>
+        <v>2.88</v>
       </c>
       <c r="P22">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="R22">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S22">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="T22">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V22">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="W22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X22">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Z22">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA22">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB22">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="AC22">
-        <v>1.55</v>
+        <v>2.62</v>
       </c>
       <c r="AD22">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AE22">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF22">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AG22">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH22">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AI22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="s">
         <v>112</v>
@@ -3279,7 +3279,7 @@
         <v>52</v>
       </c>
       <c r="C23" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D23" t="s">
         <v>66</v>
@@ -3306,76 +3306,76 @@
         <v>111</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI23">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ23" t="s">
         <v>112</v>

--- a/jogos_2025-07-18.xlsx
+++ b/jogos_2025-07-18.xlsx
@@ -202,12 +202,12 @@
     <t>Argentina Primera División</t>
   </si>
   <si>
+    <t>Canada Canadian Premier League</t>
+  </si>
+  <si>
     <t>USA USL Championship</t>
   </si>
   <si>
-    <t>Canada Canadian Premier League</t>
-  </si>
-  <si>
     <t>Chile Primera División</t>
   </si>
   <si>
@@ -256,15 +256,15 @@
     <t>Boca Juniors</t>
   </si>
   <si>
+    <t>Forge FC</t>
+  </si>
+  <si>
+    <t>Atlético Ottawa</t>
+  </si>
+  <si>
     <t>Detroit City FC</t>
   </si>
   <si>
-    <t>Atlético Ottawa</t>
-  </si>
-  <si>
-    <t>Forge FC</t>
-  </si>
-  <si>
     <t>Everton</t>
   </si>
   <si>
@@ -322,13 +322,13 @@
     <t>Unión Santa Fe</t>
   </si>
   <si>
+    <t>Pacific FC</t>
+  </si>
+  <si>
+    <t>HFX Wanderers FC</t>
+  </si>
+  <si>
     <t>Pittsburgh Riverhounds</t>
-  </si>
-  <si>
-    <t>HFX Wanderers FC</t>
-  </si>
-  <si>
-    <t>Pacific FC</t>
   </si>
   <si>
     <t>Deportes Limache</t>
@@ -2378,76 +2378,76 @@
         <v>111</v>
       </c>
       <c r="L15">
-        <v>2.51</v>
+        <v>1.47</v>
       </c>
       <c r="M15">
+        <v>3.8</v>
+      </c>
+      <c r="N15">
+        <v>5.4</v>
+      </c>
+      <c r="O15">
+        <v>1.4</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>3.5</v>
+      </c>
+      <c r="R15">
+        <v>1.36</v>
+      </c>
+      <c r="S15">
         <v>3</v>
       </c>
-      <c r="N15">
-        <v>2.84</v>
-      </c>
-      <c r="O15">
-        <v>1.99</v>
-      </c>
-      <c r="P15">
-        <v>6.6</v>
-      </c>
-      <c r="Q15">
-        <v>2.16</v>
-      </c>
-      <c r="R15">
-        <v>1.53</v>
-      </c>
-      <c r="S15">
-        <v>2.4</v>
-      </c>
       <c r="T15">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="U15">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="V15">
-        <v>9.6</v>
+        <v>6.5</v>
       </c>
       <c r="W15">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X15">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y15">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Z15">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA15">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>2.37</v>
+        <v>1.9</v>
       </c>
       <c r="AC15">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="AD15">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AE15">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AG15">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AH15">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AI15">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="s">
         <v>112</v>
@@ -2467,7 +2467,7 @@
         <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D16" t="s">
         <v>66</v>
@@ -2610,76 +2610,76 @@
         <v>111</v>
       </c>
       <c r="L17">
-        <v>1.47</v>
+        <v>2.51</v>
       </c>
       <c r="M17">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="N17">
-        <v>5.4</v>
+        <v>2.84</v>
       </c>
       <c r="O17">
-        <v>1.4</v>
+        <v>1.99</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="Q17">
-        <v>3.5</v>
+        <v>2.16</v>
       </c>
       <c r="R17">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="S17">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="T17">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="U17">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="V17">
-        <v>6.5</v>
+        <v>9.6</v>
       </c>
       <c r="W17">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB17">
-        <v>1.9</v>
+        <v>2.37</v>
       </c>
       <c r="AC17">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF17">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AG17">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ17" t="s">
         <v>112</v>
@@ -2815,7 +2815,7 @@
         <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D19" t="s">
         <v>66</v>

--- a/jogos_2025-07-18.xlsx
+++ b/jogos_2025-07-18.xlsx
@@ -187,12 +187,12 @@
     <t>China China League One</t>
   </si>
   <si>
+    <t>Finland Veikkausliiga</t>
+  </si>
+  <si>
     <t>Kazakhstan Kazakhstan Premier League</t>
   </si>
   <si>
-    <t>Finland Veikkausliiga</t>
-  </si>
-  <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
@@ -205,12 +205,12 @@
     <t>Canada Canadian Premier League</t>
   </si>
   <si>
+    <t>Chile Primera División</t>
+  </si>
+  <si>
     <t>USA USL Championship</t>
   </si>
   <si>
-    <t>Chile Primera División</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
@@ -223,12 +223,12 @@
     <t>Sydney II</t>
   </si>
   <si>
+    <t>Suwon</t>
+  </si>
+  <si>
     <t>Daegu</t>
   </si>
   <si>
-    <t>Suwon</t>
-  </si>
-  <si>
     <t>Wuhan Three Towns</t>
   </si>
   <si>
@@ -241,12 +241,12 @@
     <t>Zhejiang FC</t>
   </si>
   <si>
+    <t>KTP</t>
+  </si>
+  <si>
     <t>Astana</t>
   </si>
   <si>
-    <t>KTP</t>
-  </si>
-  <si>
     <t>Sarpsborg 08</t>
   </si>
   <si>
@@ -256,30 +256,30 @@
     <t>Boca Juniors</t>
   </si>
   <si>
+    <t>Atlético Ottawa</t>
+  </si>
+  <si>
     <t>Forge FC</t>
   </si>
   <si>
-    <t>Atlético Ottawa</t>
+    <t>Everton</t>
   </si>
   <si>
     <t>Detroit City FC</t>
   </si>
   <si>
-    <t>Everton</t>
-  </si>
-  <si>
     <t>North Carolina FC</t>
   </si>
   <si>
     <t>Huntsville City</t>
   </si>
   <si>
+    <t>Sporting KC II</t>
+  </si>
+  <si>
     <t>Ferroviária</t>
   </si>
   <si>
-    <t>Sporting KC II</t>
-  </si>
-  <si>
     <t>Atlético Tucumán</t>
   </si>
   <si>
@@ -289,12 +289,12 @@
     <t>Western Sydney W. II</t>
   </si>
   <si>
+    <t>Gwangju</t>
+  </si>
+  <si>
     <t>Sangju Sangmu</t>
   </si>
   <si>
-    <t>Gwangju</t>
-  </si>
-  <si>
     <t>Qingdao Youth Island</t>
   </si>
   <si>
@@ -307,12 +307,12 @@
     <t>Yunnan Yukun</t>
   </si>
   <si>
+    <t>Inter Turku</t>
+  </si>
+  <si>
     <t>Turan Turkistan</t>
   </si>
   <si>
-    <t>Inter Turku</t>
-  </si>
-  <si>
     <t>Rosenborg</t>
   </si>
   <si>
@@ -322,28 +322,28 @@
     <t>Unión Santa Fe</t>
   </si>
   <si>
+    <t>HFX Wanderers FC</t>
+  </si>
+  <si>
     <t>Pacific FC</t>
   </si>
   <si>
-    <t>HFX Wanderers FC</t>
+    <t>Deportes Limache</t>
   </si>
   <si>
     <t>Pittsburgh Riverhounds</t>
   </si>
   <si>
-    <t>Deportes Limache</t>
-  </si>
-  <si>
     <t>Indy Eleven</t>
   </si>
   <si>
     <t>Columbus Crew II</t>
   </si>
   <si>
+    <t>North Texas</t>
+  </si>
+  <si>
     <t>Athletic Club</t>
-  </si>
-  <si>
-    <t>North Texas</t>
   </si>
   <si>
     <t>Central Córdoba SdE</t>
@@ -870,13 +870,13 @@
         <v>111</v>
       </c>
       <c r="L2">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="M2">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="N2">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="O2">
         <v>3.22</v>
@@ -918,10 +918,10 @@
         <v>6.6</v>
       </c>
       <c r="AB2">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AC2">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="AD2">
         <v>1.83</v>
@@ -989,10 +989,10 @@
         <v>1.67</v>
       </c>
       <c r="M3">
-        <v>4.01</v>
+        <v>4.1</v>
       </c>
       <c r="N3">
-        <v>3.77</v>
+        <v>3.93</v>
       </c>
       <c r="O3">
         <v>1.68</v>
@@ -1004,22 +1004,22 @@
         <v>2.12</v>
       </c>
       <c r="R3">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="S3">
         <v>4.5</v>
       </c>
       <c r="T3">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="U3">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="V3">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="W3">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X3">
         <v>1</v>
@@ -1028,34 +1028,34 @@
         <v>12</v>
       </c>
       <c r="Z3">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AA3">
         <v>6</v>
       </c>
       <c r="AB3">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AC3">
-        <v>3.14</v>
+        <v>2.35</v>
       </c>
       <c r="AD3">
-        <v>1.81</v>
+        <v>2.02</v>
       </c>
       <c r="AE3">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AF3">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AG3">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="AH3">
-        <v>2.74</v>
+        <v>3.2</v>
       </c>
       <c r="AI3">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AJ3" t="s">
         <v>112</v>
@@ -1102,76 +1102,76 @@
         <v>111</v>
       </c>
       <c r="L4">
-        <v>3.47</v>
+        <v>2.67</v>
       </c>
       <c r="M4">
-        <v>3.45</v>
+        <v>3.03</v>
       </c>
       <c r="N4">
-        <v>1.85</v>
+        <v>2.41</v>
       </c>
       <c r="O4">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="P4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q4">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="R4">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S4">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="T4">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="U4">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="V4">
-        <v>5.65</v>
+        <v>7</v>
       </c>
       <c r="W4">
         <v>1.08</v>
       </c>
       <c r="X4">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z4">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AA4">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="AB4">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AC4">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AD4">
-        <v>2.6</v>
+        <v>3.45</v>
       </c>
       <c r="AE4">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AF4">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AG4">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AH4">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="AI4">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AJ4" t="s">
         <v>112</v>
@@ -1218,76 +1218,76 @@
         <v>111</v>
       </c>
       <c r="L5">
-        <v>2.67</v>
+        <v>3.47</v>
       </c>
       <c r="M5">
-        <v>3.03</v>
+        <v>3.45</v>
       </c>
       <c r="N5">
-        <v>2.41</v>
+        <v>1.85</v>
       </c>
       <c r="O5">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="P5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="R5">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S5">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="T5">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="U5">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="V5">
-        <v>7</v>
+        <v>5.65</v>
       </c>
       <c r="W5">
         <v>1.08</v>
       </c>
       <c r="X5">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z5">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AA5">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="AB5">
-        <v>1.95</v>
+        <v>1.59</v>
       </c>
       <c r="AC5">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AD5">
-        <v>3.45</v>
+        <v>2.6</v>
       </c>
       <c r="AE5">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AF5">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AG5">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH5">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="AI5">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AJ5" t="s">
         <v>112</v>
@@ -1334,13 +1334,13 @@
         <v>111</v>
       </c>
       <c r="L6">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="M6">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="N6">
-        <v>3.2</v>
+        <v>3.11</v>
       </c>
       <c r="O6">
         <v>1.72</v>
@@ -1450,19 +1450,19 @@
         <v>111</v>
       </c>
       <c r="L7">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="M7">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N7">
-        <v>4.11</v>
+        <v>3.65</v>
       </c>
       <c r="O7">
         <v>1.44</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q7">
         <v>3</v>
@@ -1471,55 +1471,55 @@
         <v>1.39</v>
       </c>
       <c r="S7">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="T7">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="U7">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V7">
         <v>7.1</v>
       </c>
       <c r="W7">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y7">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Z7">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AA7">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AB7">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC7">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AD7">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AE7">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF7">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AG7">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AH7">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="AI7">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AJ7" t="s">
         <v>112</v>
@@ -1682,13 +1682,13 @@
         <v>111</v>
       </c>
       <c r="L9">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="M9">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="N9">
-        <v>3.85</v>
+        <v>3.36</v>
       </c>
       <c r="O9">
         <v>1.63</v>
@@ -1730,10 +1730,10 @@
         <v>5.7</v>
       </c>
       <c r="AB9">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AC9">
-        <v>2.25</v>
+        <v>2.65</v>
       </c>
       <c r="AD9">
         <v>2.1</v>
@@ -1798,76 +1798,76 @@
         <v>111</v>
       </c>
       <c r="L10">
-        <v>1.06</v>
+        <v>5.4</v>
       </c>
       <c r="M10">
-        <v>8.199999999999999</v>
+        <v>3.76</v>
       </c>
       <c r="N10">
-        <v>23</v>
+        <v>1.49</v>
       </c>
       <c r="O10">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="P10">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Q10">
-        <v>10</v>
+        <v>1.3</v>
       </c>
       <c r="R10">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="S10">
-        <v>3.48</v>
+        <v>3.8</v>
       </c>
       <c r="T10">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="U10">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="V10">
-        <v>5.2</v>
+        <v>4.45</v>
       </c>
       <c r="W10">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X10">
         <v>1</v>
       </c>
       <c r="Y10">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Z10">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AA10">
-        <v>4.35</v>
+        <v>5</v>
       </c>
       <c r="AB10">
         <v>1.57</v>
       </c>
       <c r="AC10">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AD10">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AE10">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AF10">
-        <v>4.65</v>
+        <v>1.72</v>
       </c>
       <c r="AG10">
-        <v>1.18</v>
+        <v>2.02</v>
       </c>
       <c r="AH10">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AI10">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AJ10" t="s">
         <v>112</v>
@@ -1914,76 +1914,76 @@
         <v>111</v>
       </c>
       <c r="L11">
-        <v>6.5</v>
+        <v>1.06</v>
       </c>
       <c r="M11">
-        <v>4.84</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N11">
-        <v>1.36</v>
+        <v>23</v>
       </c>
       <c r="O11">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="P11">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Q11">
-        <v>1.3</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S11">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="T11">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="U11">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="V11">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="W11">
         <v>1.13</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y11">
         <v>12</v>
       </c>
       <c r="Z11">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AA11">
-        <v>5.55</v>
+        <v>4.2</v>
       </c>
       <c r="AB11">
+        <v>1.6</v>
+      </c>
+      <c r="AC11">
+        <v>2.29</v>
+      </c>
+      <c r="AD11">
+        <v>2.33</v>
+      </c>
+      <c r="AE11">
         <v>1.5</v>
       </c>
-      <c r="AC11">
-        <v>2.5</v>
-      </c>
-      <c r="AD11">
-        <v>2.2</v>
-      </c>
-      <c r="AE11">
-        <v>1.6</v>
-      </c>
       <c r="AF11">
-        <v>1.7</v>
+        <v>4.6</v>
       </c>
       <c r="AG11">
-        <v>2.1</v>
+        <v>1.18</v>
       </c>
       <c r="AH11">
-        <v>3.4</v>
+        <v>3.98</v>
       </c>
       <c r="AI11">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AJ11" t="s">
         <v>112</v>
@@ -2084,10 +2084,10 @@
         <v>2.2</v>
       </c>
       <c r="AD12">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="AE12">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AF12">
         <v>1.48</v>
@@ -2146,13 +2146,13 @@
         <v>111</v>
       </c>
       <c r="L13">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="M13">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="N13">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="O13">
         <v>1.6</v>
@@ -2164,58 +2164,58 @@
         <v>2.95</v>
       </c>
       <c r="R13">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="S13">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="T13">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="U13">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="V13">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="W13">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="X13">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>7.02</v>
       </c>
       <c r="Z13">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AA13">
         <v>2.45</v>
       </c>
       <c r="AB13">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AC13">
         <v>1.5</v>
       </c>
       <c r="AD13">
-        <v>4.7</v>
+        <v>5.03</v>
       </c>
       <c r="AE13">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF13">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AG13">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AH13">
         <v>9.5</v>
       </c>
       <c r="AI13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AJ13" t="s">
         <v>112</v>
@@ -2378,76 +2378,76 @@
         <v>111</v>
       </c>
       <c r="L15">
-        <v>1.47</v>
+        <v>1.9</v>
       </c>
       <c r="M15">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N15">
-        <v>5.4</v>
+        <v>3.7</v>
       </c>
       <c r="O15">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="Q15">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="R15">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S15">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="T15">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U15">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V15">
+        <v>7</v>
+      </c>
+      <c r="W15">
+        <v>1.07</v>
+      </c>
+      <c r="X15">
+        <v>1.02</v>
+      </c>
+      <c r="Y15">
+        <v>8.75</v>
+      </c>
+      <c r="Z15">
+        <v>1.29</v>
+      </c>
+      <c r="AA15">
+        <v>3.25</v>
+      </c>
+      <c r="AB15">
+        <v>1.73</v>
+      </c>
+      <c r="AC15">
+        <v>1.91</v>
+      </c>
+      <c r="AD15">
+        <v>3.2</v>
+      </c>
+      <c r="AE15">
+        <v>1.26</v>
+      </c>
+      <c r="AF15">
+        <v>1.73</v>
+      </c>
+      <c r="AG15">
+        <v>1.95</v>
+      </c>
+      <c r="AH15">
         <v>6.5</v>
       </c>
-      <c r="W15">
-        <v>1.1</v>
-      </c>
-      <c r="X15">
-        <v>0</v>
-      </c>
-      <c r="Y15">
-        <v>0</v>
-      </c>
-      <c r="Z15">
-        <v>0</v>
-      </c>
-      <c r="AA15">
-        <v>0</v>
-      </c>
-      <c r="AB15">
-        <v>1.9</v>
-      </c>
-      <c r="AC15">
-        <v>1.9</v>
-      </c>
-      <c r="AD15">
-        <v>0</v>
-      </c>
-      <c r="AE15">
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <v>2.1</v>
-      </c>
-      <c r="AG15">
-        <v>1.67</v>
-      </c>
-      <c r="AH15">
-        <v>0</v>
-      </c>
       <c r="AI15">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ15" t="s">
         <v>112</v>
@@ -2494,76 +2494,76 @@
         <v>111</v>
       </c>
       <c r="L16">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="M16">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="N16">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="O16">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="R16">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S16">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="T16">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U16">
         <v>1.44</v>
       </c>
       <c r="V16">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W16">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB16">
         <v>1.8</v>
       </c>
       <c r="AC16">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF16">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG16">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ16" t="s">
         <v>112</v>
@@ -2610,76 +2610,76 @@
         <v>111</v>
       </c>
       <c r="L17">
-        <v>2.51</v>
+        <v>2.15</v>
       </c>
       <c r="M17">
+        <v>3.5</v>
+      </c>
+      <c r="N17">
+        <v>3.1</v>
+      </c>
+      <c r="O17">
+        <v>1.78</v>
+      </c>
+      <c r="P17">
+        <v>10</v>
+      </c>
+      <c r="Q17">
+        <v>2.2</v>
+      </c>
+      <c r="R17">
+        <v>1.35</v>
+      </c>
+      <c r="S17">
+        <v>2.9</v>
+      </c>
+      <c r="T17">
+        <v>2.6</v>
+      </c>
+      <c r="U17">
+        <v>1.43</v>
+      </c>
+      <c r="V17">
+        <v>6.5</v>
+      </c>
+      <c r="W17">
+        <v>1.1</v>
+      </c>
+      <c r="X17">
+        <v>1.05</v>
+      </c>
+      <c r="Y17">
+        <v>8.5</v>
+      </c>
+      <c r="Z17">
+        <v>1.25</v>
+      </c>
+      <c r="AA17">
+        <v>3.6</v>
+      </c>
+      <c r="AB17">
+        <v>1.77</v>
+      </c>
+      <c r="AC17">
+        <v>1.9</v>
+      </c>
+      <c r="AD17">
         <v>3</v>
       </c>
-      <c r="N17">
-        <v>2.84</v>
-      </c>
-      <c r="O17">
-        <v>1.99</v>
-      </c>
-      <c r="P17">
-        <v>6.6</v>
-      </c>
-      <c r="Q17">
-        <v>2.16</v>
-      </c>
-      <c r="R17">
-        <v>1.53</v>
-      </c>
-      <c r="S17">
-        <v>2.4</v>
-      </c>
-      <c r="T17">
-        <v>3.4</v>
-      </c>
-      <c r="U17">
-        <v>1.3</v>
-      </c>
-      <c r="V17">
-        <v>9.6</v>
-      </c>
-      <c r="W17">
-        <v>1.05</v>
-      </c>
-      <c r="X17">
+      <c r="AE17">
+        <v>1.36</v>
+      </c>
+      <c r="AF17">
+        <v>1.68</v>
+      </c>
+      <c r="AG17">
+        <v>2.05</v>
+      </c>
+      <c r="AH17">
+        <v>5.4</v>
+      </c>
+      <c r="AI17">
         <v>1.09</v>
-      </c>
-      <c r="Y17">
-        <v>6</v>
-      </c>
-      <c r="Z17">
-        <v>1.5</v>
-      </c>
-      <c r="AA17">
-        <v>2.4</v>
-      </c>
-      <c r="AB17">
-        <v>2.37</v>
-      </c>
-      <c r="AC17">
-        <v>1.53</v>
-      </c>
-      <c r="AD17">
-        <v>4.55</v>
-      </c>
-      <c r="AE17">
-        <v>1.18</v>
-      </c>
-      <c r="AF17">
-        <v>1.97</v>
-      </c>
-      <c r="AG17">
-        <v>1.71</v>
-      </c>
-      <c r="AH17">
-        <v>8.5</v>
-      </c>
-      <c r="AI17">
-        <v>1.04</v>
       </c>
       <c r="AJ17" t="s">
         <v>112</v>
@@ -2726,76 +2726,76 @@
         <v>111</v>
       </c>
       <c r="L18">
-        <v>2.15</v>
+        <v>2.91</v>
       </c>
       <c r="M18">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="N18">
-        <v>3.1</v>
+        <v>2.43</v>
       </c>
       <c r="O18">
-        <v>1.78</v>
+        <v>1.99</v>
       </c>
       <c r="P18">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="Q18">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R18">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="S18">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="T18">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="U18">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="V18">
-        <v>6.5</v>
+        <v>11</v>
       </c>
       <c r="W18">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X18">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y18">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="Z18">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AA18">
-        <v>3.6</v>
+        <v>2.51</v>
       </c>
       <c r="AB18">
-        <v>1.77</v>
+        <v>2.5</v>
       </c>
       <c r="AC18">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AD18">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="AE18">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AF18">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AG18">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AH18">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="AI18">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AJ18" t="s">
         <v>112</v>
@@ -2815,7 +2815,7 @@
         <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D19" t="s">
         <v>66</v>
@@ -2842,13 +2842,13 @@
         <v>111</v>
       </c>
       <c r="L19">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="M19">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="N19">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O19">
         <v>1.7</v>
@@ -2860,7 +2860,7 @@
         <v>2.29</v>
       </c>
       <c r="R19">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S19">
         <v>2.84</v>
@@ -2872,25 +2872,25 @@
         <v>1.4</v>
       </c>
       <c r="V19">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="W19">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X19">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
         <v>8.800000000000001</v>
       </c>
       <c r="Z19">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AA19">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="AB19">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AC19">
         <v>1.8</v>
@@ -2899,19 +2899,19 @@
         <v>3.4</v>
       </c>
       <c r="AE19">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF19">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG19">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AH19">
         <v>6.5</v>
       </c>
       <c r="AI19">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AJ19" t="s">
         <v>112</v>
@@ -2976,28 +2976,28 @@
         <v>3</v>
       </c>
       <c r="R20">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="S20">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="T20">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="U20">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z20">
         <v>1.14</v>
@@ -3006,28 +3006,28 @@
         <v>4.45</v>
       </c>
       <c r="AB20">
+        <v>1.55</v>
+      </c>
+      <c r="AC20">
+        <v>2.37</v>
+      </c>
+      <c r="AD20">
+        <v>2.17</v>
+      </c>
+      <c r="AE20">
         <v>1.6</v>
       </c>
-      <c r="AC20">
-        <v>2.18</v>
-      </c>
-      <c r="AD20">
-        <v>2.43</v>
-      </c>
-      <c r="AE20">
-        <v>1.44</v>
-      </c>
       <c r="AF20">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AG20">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="AH20">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AI20">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AJ20" t="s">
         <v>112</v>
@@ -3047,7 +3047,7 @@
         <v>52</v>
       </c>
       <c r="C21" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D21" t="s">
         <v>66</v>
@@ -3074,76 +3074,76 @@
         <v>111</v>
       </c>
       <c r="L21">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M21">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="N21">
-        <v>3.14</v>
+        <v>1.67</v>
       </c>
       <c r="O21">
-        <v>1.83</v>
+        <v>2.88</v>
       </c>
       <c r="P21">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="Q21">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="R21">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="S21">
-        <v>2.39</v>
+        <v>3.8</v>
       </c>
       <c r="T21">
-        <v>3.5</v>
+        <v>2.14</v>
       </c>
       <c r="U21">
-        <v>1.26</v>
+        <v>1.61</v>
       </c>
       <c r="V21">
-        <v>9.9</v>
+        <v>4</v>
       </c>
       <c r="W21">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="X21">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Z21">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="AA21">
-        <v>2.7</v>
+        <v>4.7</v>
       </c>
       <c r="AB21">
-        <v>2.55</v>
+        <v>1.39</v>
       </c>
       <c r="AC21">
-        <v>1.5</v>
+        <v>2.75</v>
       </c>
       <c r="AD21">
-        <v>4.85</v>
+        <v>2.05</v>
       </c>
       <c r="AE21">
-        <v>1.17</v>
+        <v>1.7</v>
       </c>
       <c r="AF21">
-        <v>2.07</v>
+        <v>1.44</v>
       </c>
       <c r="AG21">
-        <v>1.67</v>
+        <v>2.6</v>
       </c>
       <c r="AH21">
-        <v>11</v>
+        <v>3.2</v>
       </c>
       <c r="AI21">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="AJ21" t="s">
         <v>112</v>
@@ -3163,7 +3163,7 @@
         <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D22" t="s">
         <v>66</v>
@@ -3190,76 +3190,76 @@
         <v>111</v>
       </c>
       <c r="L22">
-        <v>5.05</v>
+        <v>2.29</v>
       </c>
       <c r="M22">
-        <v>4.35</v>
+        <v>3.05</v>
       </c>
       <c r="N22">
-        <v>1.49</v>
+        <v>2.98</v>
       </c>
       <c r="O22">
-        <v>2.88</v>
+        <v>1.83</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Q22">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>6.84</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AB22">
-        <v>1.44</v>
+        <v>2.47</v>
       </c>
       <c r="AC22">
-        <v>2.62</v>
+        <v>1.5</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH22">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ22" t="s">
         <v>112</v>

--- a/jogos_2025-07-18.xlsx
+++ b/jogos_2025-07-18.xlsx
@@ -187,12 +187,12 @@
     <t>China China League One</t>
   </si>
   <si>
+    <t>Kazakhstan Kazakhstan Premier League</t>
+  </si>
+  <si>
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
-    <t>Kazakhstan Kazakhstan Premier League</t>
-  </si>
-  <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
@@ -202,12 +202,12 @@
     <t>Argentina Primera División</t>
   </si>
   <si>
+    <t>Chile Primera División</t>
+  </si>
+  <si>
     <t>Canada Canadian Premier League</t>
   </si>
   <si>
-    <t>Chile Primera División</t>
-  </si>
-  <si>
     <t>USA USL Championship</t>
   </si>
   <si>
@@ -241,12 +241,12 @@
     <t>Zhejiang FC</t>
   </si>
   <si>
+    <t>Astana</t>
+  </si>
+  <si>
     <t>KTP</t>
   </si>
   <si>
-    <t>Astana</t>
-  </si>
-  <si>
     <t>Sarpsborg 08</t>
   </si>
   <si>
@@ -256,33 +256,33 @@
     <t>Boca Juniors</t>
   </si>
   <si>
+    <t>Everton</t>
+  </si>
+  <si>
+    <t>Forge FC</t>
+  </si>
+  <si>
+    <t>Detroit City FC</t>
+  </si>
+  <si>
     <t>Atlético Ottawa</t>
   </si>
   <si>
-    <t>Forge FC</t>
-  </si>
-  <si>
-    <t>Everton</t>
-  </si>
-  <si>
-    <t>Detroit City FC</t>
-  </si>
-  <si>
     <t>North Carolina FC</t>
   </si>
   <si>
     <t>Huntsville City</t>
   </si>
   <si>
+    <t>Atlético Tucumán</t>
+  </si>
+  <si>
     <t>Sporting KC II</t>
   </si>
   <si>
     <t>Ferroviária</t>
   </si>
   <si>
-    <t>Atlético Tucumán</t>
-  </si>
-  <si>
     <t>Shanghai SIPG</t>
   </si>
   <si>
@@ -307,12 +307,12 @@
     <t>Yunnan Yukun</t>
   </si>
   <si>
+    <t>Turan Turkistan</t>
+  </si>
+  <si>
     <t>Inter Turku</t>
   </si>
   <si>
-    <t>Turan Turkistan</t>
-  </si>
-  <si>
     <t>Rosenborg</t>
   </si>
   <si>
@@ -322,31 +322,31 @@
     <t>Unión Santa Fe</t>
   </si>
   <si>
+    <t>Deportes Limache</t>
+  </si>
+  <si>
+    <t>Pacific FC</t>
+  </si>
+  <si>
+    <t>Pittsburgh Riverhounds</t>
+  </si>
+  <si>
     <t>HFX Wanderers FC</t>
   </si>
   <si>
-    <t>Pacific FC</t>
-  </si>
-  <si>
-    <t>Deportes Limache</t>
-  </si>
-  <si>
-    <t>Pittsburgh Riverhounds</t>
-  </si>
-  <si>
     <t>Indy Eleven</t>
   </si>
   <si>
     <t>Columbus Crew II</t>
   </si>
   <si>
+    <t>Central Córdoba SdE</t>
+  </si>
+  <si>
     <t>North Texas</t>
   </si>
   <si>
     <t>Athletic Club</t>
-  </si>
-  <si>
-    <t>Central Córdoba SdE</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -986,13 +986,13 @@
         <v>111</v>
       </c>
       <c r="L3">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="M3">
-        <v>4.1</v>
+        <v>3.79</v>
       </c>
       <c r="N3">
-        <v>3.93</v>
+        <v>3.87</v>
       </c>
       <c r="O3">
         <v>1.68</v>
@@ -1007,13 +1007,13 @@
         <v>1.18</v>
       </c>
       <c r="S3">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="T3">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="U3">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="V3">
         <v>3.7</v>
@@ -1031,31 +1031,31 @@
         <v>1.07</v>
       </c>
       <c r="AA3">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AB3">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AC3">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="AD3">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AE3">
         <v>1.7</v>
       </c>
       <c r="AF3">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AG3">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="AH3">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AI3">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AJ3" t="s">
         <v>112</v>
@@ -1798,40 +1798,40 @@
         <v>111</v>
       </c>
       <c r="L10">
-        <v>5.4</v>
+        <v>1.06</v>
       </c>
       <c r="M10">
-        <v>3.76</v>
+        <v>8.6</v>
       </c>
       <c r="N10">
-        <v>1.49</v>
+        <v>25</v>
       </c>
       <c r="O10">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="P10">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Q10">
-        <v>1.3</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>1.22</v>
       </c>
       <c r="S10">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="T10">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="U10">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="V10">
-        <v>4.45</v>
+        <v>5</v>
       </c>
       <c r="W10">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X10">
         <v>1</v>
@@ -1840,34 +1840,34 @@
         <v>17</v>
       </c>
       <c r="Z10">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AA10">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AB10">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AC10">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AD10">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AE10">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AF10">
-        <v>1.72</v>
+        <v>3.3</v>
       </c>
       <c r="AG10">
-        <v>2.02</v>
+        <v>1.3</v>
       </c>
       <c r="AH10">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AI10">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AJ10" t="s">
         <v>112</v>
@@ -1914,76 +1914,76 @@
         <v>111</v>
       </c>
       <c r="L11">
-        <v>1.06</v>
+        <v>8</v>
       </c>
       <c r="M11">
-        <v>8.199999999999999</v>
+        <v>5.05</v>
       </c>
       <c r="N11">
-        <v>23</v>
+        <v>1.33</v>
       </c>
       <c r="O11">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="P11">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Q11">
-        <v>10</v>
+        <v>1.3</v>
       </c>
       <c r="R11">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="S11">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="T11">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="U11">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="V11">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="W11">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X11">
         <v>1</v>
       </c>
       <c r="Y11">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Z11">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AA11">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AB11">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="AC11">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="AD11">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="AE11">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AF11">
-        <v>4.6</v>
+        <v>1.72</v>
       </c>
       <c r="AG11">
-        <v>1.18</v>
+        <v>2.02</v>
       </c>
       <c r="AH11">
-        <v>3.98</v>
+        <v>3.6</v>
       </c>
       <c r="AI11">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AJ11" t="s">
         <v>112</v>
@@ -2378,76 +2378,76 @@
         <v>111</v>
       </c>
       <c r="L15">
+        <v>2.15</v>
+      </c>
+      <c r="M15">
+        <v>3.5</v>
+      </c>
+      <c r="N15">
+        <v>3.1</v>
+      </c>
+      <c r="O15">
+        <v>1.78</v>
+      </c>
+      <c r="P15">
+        <v>10</v>
+      </c>
+      <c r="Q15">
+        <v>2.2</v>
+      </c>
+      <c r="R15">
+        <v>1.35</v>
+      </c>
+      <c r="S15">
+        <v>2.9</v>
+      </c>
+      <c r="T15">
+        <v>2.6</v>
+      </c>
+      <c r="U15">
+        <v>1.43</v>
+      </c>
+      <c r="V15">
+        <v>6.5</v>
+      </c>
+      <c r="W15">
+        <v>1.1</v>
+      </c>
+      <c r="X15">
+        <v>1.05</v>
+      </c>
+      <c r="Y15">
+        <v>8.5</v>
+      </c>
+      <c r="Z15">
+        <v>1.25</v>
+      </c>
+      <c r="AA15">
+        <v>3.6</v>
+      </c>
+      <c r="AB15">
+        <v>1.77</v>
+      </c>
+      <c r="AC15">
         <v>1.9</v>
       </c>
-      <c r="M15">
-        <v>3.3</v>
-      </c>
-      <c r="N15">
-        <v>3.7</v>
-      </c>
-      <c r="O15">
-        <v>1.57</v>
-      </c>
-      <c r="P15">
-        <v>8.75</v>
-      </c>
-      <c r="Q15">
-        <v>2.6</v>
-      </c>
-      <c r="R15">
-        <v>1.38</v>
-      </c>
-      <c r="S15">
-        <v>2.65</v>
-      </c>
-      <c r="T15">
-        <v>2.8</v>
-      </c>
-      <c r="U15">
-        <v>1.38</v>
-      </c>
-      <c r="V15">
-        <v>7</v>
-      </c>
-      <c r="W15">
-        <v>1.07</v>
-      </c>
-      <c r="X15">
-        <v>1.02</v>
-      </c>
-      <c r="Y15">
-        <v>8.75</v>
-      </c>
-      <c r="Z15">
-        <v>1.29</v>
-      </c>
-      <c r="AA15">
-        <v>3.25</v>
-      </c>
-      <c r="AB15">
-        <v>1.73</v>
-      </c>
-      <c r="AC15">
-        <v>1.91</v>
-      </c>
       <c r="AD15">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AE15">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AF15">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AG15">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH15">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="AI15">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AJ15" t="s">
         <v>112</v>
@@ -2467,7 +2467,7 @@
         <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s">
         <v>66</v>
@@ -2494,13 +2494,13 @@
         <v>111</v>
       </c>
       <c r="L16">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="M16">
-        <v>3.65</v>
+        <v>3.84</v>
       </c>
       <c r="N16">
-        <v>4.9</v>
+        <v>5.06</v>
       </c>
       <c r="O16">
         <v>1.4</v>
@@ -2512,7 +2512,7 @@
         <v>3.5</v>
       </c>
       <c r="R16">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S16">
         <v>2.99</v>
@@ -2527,7 +2527,7 @@
         <v>6.5</v>
       </c>
       <c r="W16">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
         <v>1.04</v>
@@ -2539,31 +2539,31 @@
         <v>1.25</v>
       </c>
       <c r="AA16">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AB16">
+        <v>1.81</v>
+      </c>
+      <c r="AC16">
+        <v>1.87</v>
+      </c>
+      <c r="AD16">
+        <v>2.92</v>
+      </c>
+      <c r="AE16">
+        <v>1.36</v>
+      </c>
+      <c r="AF16">
         <v>1.8</v>
       </c>
-      <c r="AC16">
-        <v>1.83</v>
-      </c>
-      <c r="AD16">
-        <v>2.88</v>
-      </c>
-      <c r="AE16">
-        <v>1.32</v>
-      </c>
-      <c r="AF16">
-        <v>1.75</v>
-      </c>
       <c r="AG16">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AH16">
         <v>5.25</v>
       </c>
       <c r="AI16">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AJ16" t="s">
         <v>112</v>
@@ -2583,7 +2583,7 @@
         <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" t="s">
         <v>66</v>
@@ -2610,76 +2610,76 @@
         <v>111</v>
       </c>
       <c r="L17">
-        <v>2.15</v>
+        <v>2.91</v>
       </c>
       <c r="M17">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="N17">
-        <v>3.1</v>
+        <v>2.43</v>
       </c>
       <c r="O17">
-        <v>1.78</v>
+        <v>1.99</v>
       </c>
       <c r="P17">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="Q17">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R17">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="S17">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="T17">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="U17">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="V17">
-        <v>6.5</v>
+        <v>11</v>
       </c>
       <c r="W17">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X17">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y17">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="Z17">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AA17">
-        <v>3.6</v>
+        <v>2.51</v>
       </c>
       <c r="AB17">
-        <v>1.77</v>
+        <v>2.5</v>
       </c>
       <c r="AC17">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AD17">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="AE17">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AF17">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AG17">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AH17">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="AI17">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AJ17" t="s">
         <v>112</v>
@@ -2699,7 +2699,7 @@
         <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D18" t="s">
         <v>66</v>
@@ -2726,76 +2726,76 @@
         <v>111</v>
       </c>
       <c r="L18">
-        <v>2.91</v>
+        <v>2.26</v>
       </c>
       <c r="M18">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N18">
-        <v>2.43</v>
+        <v>2.87</v>
       </c>
       <c r="O18">
-        <v>1.99</v>
+        <v>1.57</v>
       </c>
       <c r="P18">
-        <v>6.6</v>
+        <v>8.75</v>
       </c>
       <c r="Q18">
-        <v>2.16</v>
+        <v>2.6</v>
       </c>
       <c r="R18">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="S18">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="T18">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="U18">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="V18">
-        <v>11</v>
+        <v>6.5</v>
       </c>
       <c r="W18">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X18">
         <v>1.06</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>8.75</v>
       </c>
       <c r="Z18">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AA18">
-        <v>2.51</v>
+        <v>3.28</v>
       </c>
       <c r="AB18">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="AC18">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AD18">
-        <v>4.9</v>
+        <v>3.14</v>
       </c>
       <c r="AE18">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="AF18">
+        <v>1.73</v>
+      </c>
+      <c r="AG18">
         <v>2</v>
       </c>
-      <c r="AG18">
-        <v>1.75</v>
-      </c>
       <c r="AH18">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="AI18">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AJ18" t="s">
         <v>112</v>
@@ -3047,7 +3047,7 @@
         <v>52</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D21" t="s">
         <v>66</v>
@@ -3074,76 +3074,76 @@
         <v>111</v>
       </c>
       <c r="L21">
+        <v>2</v>
+      </c>
+      <c r="M21">
+        <v>3.25</v>
+      </c>
+      <c r="N21">
+        <v>3.9</v>
+      </c>
+      <c r="O21">
+        <v>1.62</v>
+      </c>
+      <c r="P21">
+        <v>6.5</v>
+      </c>
+      <c r="Q21">
+        <v>2.75</v>
+      </c>
+      <c r="R21">
+        <v>1.5</v>
+      </c>
+      <c r="S21">
+        <v>2.5</v>
+      </c>
+      <c r="T21">
         <v>3.4</v>
       </c>
-      <c r="M21">
-        <v>4.4</v>
-      </c>
-      <c r="N21">
-        <v>1.67</v>
-      </c>
-      <c r="O21">
-        <v>2.88</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <v>1.4</v>
-      </c>
-      <c r="R21">
-        <v>1.22</v>
-      </c>
-      <c r="S21">
-        <v>3.8</v>
-      </c>
-      <c r="T21">
-        <v>2.14</v>
-      </c>
       <c r="U21">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="V21">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="W21">
+        <v>1.06</v>
+      </c>
+      <c r="X21">
+        <v>1.1</v>
+      </c>
+      <c r="Y21">
+        <v>6.5</v>
+      </c>
+      <c r="Z21">
+        <v>1.45</v>
+      </c>
+      <c r="AA21">
+        <v>2.7</v>
+      </c>
+      <c r="AB21">
+        <v>2.35</v>
+      </c>
+      <c r="AC21">
+        <v>1.57</v>
+      </c>
+      <c r="AD21">
+        <v>4.33</v>
+      </c>
+      <c r="AE21">
         <v>1.2</v>
       </c>
-      <c r="X21">
-        <v>0</v>
-      </c>
-      <c r="Y21">
-        <v>0</v>
-      </c>
-      <c r="Z21">
-        <v>1.14</v>
-      </c>
-      <c r="AA21">
-        <v>4.7</v>
-      </c>
-      <c r="AB21">
-        <v>1.39</v>
-      </c>
-      <c r="AC21">
-        <v>2.75</v>
-      </c>
-      <c r="AD21">
+      <c r="AF21">
         <v>2.05</v>
       </c>
-      <c r="AE21">
+      <c r="AG21">
         <v>1.7</v>
       </c>
-      <c r="AF21">
-        <v>1.44</v>
-      </c>
-      <c r="AG21">
-        <v>2.6</v>
-      </c>
       <c r="AH21">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="AI21">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="AJ21" t="s">
         <v>112</v>
@@ -3163,7 +3163,7 @@
         <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D22" t="s">
         <v>66</v>
@@ -3190,76 +3190,76 @@
         <v>111</v>
       </c>
       <c r="L22">
-        <v>2.29</v>
+        <v>3.4</v>
       </c>
       <c r="M22">
-        <v>3.05</v>
+        <v>4.4</v>
       </c>
       <c r="N22">
-        <v>2.98</v>
+        <v>1.67</v>
       </c>
       <c r="O22">
-        <v>1.83</v>
+        <v>2.88</v>
       </c>
       <c r="P22">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="R22">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="S22">
-        <v>2.47</v>
+        <v>3.8</v>
       </c>
       <c r="T22">
-        <v>3.55</v>
+        <v>2.14</v>
       </c>
       <c r="U22">
-        <v>1.29</v>
+        <v>1.61</v>
       </c>
       <c r="V22">
-        <v>9.9</v>
+        <v>4</v>
       </c>
       <c r="W22">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="X22">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y22">
-        <v>6.84</v>
+        <v>0</v>
       </c>
       <c r="Z22">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="AA22">
-        <v>2.47</v>
+        <v>4.7</v>
       </c>
       <c r="AB22">
-        <v>2.47</v>
+        <v>1.39</v>
       </c>
       <c r="AC22">
-        <v>1.5</v>
+        <v>2.75</v>
       </c>
       <c r="AD22">
-        <v>4.75</v>
+        <v>2.05</v>
       </c>
       <c r="AE22">
-        <v>1.17</v>
+        <v>1.7</v>
       </c>
       <c r="AF22">
-        <v>2.17</v>
+        <v>1.44</v>
       </c>
       <c r="AG22">
-        <v>1.64</v>
+        <v>2.6</v>
       </c>
       <c r="AH22">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="AI22">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="AJ22" t="s">
         <v>112</v>
@@ -3279,7 +3279,7 @@
         <v>52</v>
       </c>
       <c r="C23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D23" t="s">
         <v>66</v>
@@ -3306,76 +3306,76 @@
         <v>111</v>
       </c>
       <c r="L23">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="M23">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="N23">
-        <v>3.9</v>
+        <v>2.98</v>
       </c>
       <c r="O23">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="P23">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q23">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="R23">
         <v>1.5</v>
       </c>
       <c r="S23">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="T23">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="U23">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V23">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="W23">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="X23">
         <v>1.1</v>
       </c>
       <c r="Y23">
-        <v>6.5</v>
+        <v>6.84</v>
       </c>
       <c r="Z23">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AA23">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="AB23">
-        <v>2.35</v>
+        <v>2.47</v>
       </c>
       <c r="AC23">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AD23">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="AE23">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF23">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AG23">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AH23">
         <v>9</v>
       </c>
       <c r="AI23">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AJ23" t="s">
         <v>112</v>

--- a/jogos_2025-07-18.xlsx
+++ b/jogos_2025-07-18.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="116">
   <si>
     <t>Date</t>
   </si>
@@ -187,12 +187,12 @@
     <t>China China League One</t>
   </si>
   <si>
+    <t>Finland Veikkausliiga</t>
+  </si>
+  <si>
     <t>Kazakhstan Kazakhstan Premier League</t>
   </si>
   <si>
-    <t>Finland Veikkausliiga</t>
-  </si>
-  <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
@@ -241,12 +241,12 @@
     <t>Zhejiang FC</t>
   </si>
   <si>
+    <t>KTP</t>
+  </si>
+  <si>
     <t>Astana</t>
   </si>
   <si>
-    <t>KTP</t>
-  </si>
-  <si>
     <t>Sarpsborg 08</t>
   </si>
   <si>
@@ -259,15 +259,15 @@
     <t>Everton</t>
   </si>
   <si>
+    <t>Atlético Ottawa</t>
+  </si>
+  <si>
+    <t>Detroit City FC</t>
+  </si>
+  <si>
     <t>Forge FC</t>
   </si>
   <si>
-    <t>Detroit City FC</t>
-  </si>
-  <si>
-    <t>Atlético Ottawa</t>
-  </si>
-  <si>
     <t>North Carolina FC</t>
   </si>
   <si>
@@ -307,12 +307,12 @@
     <t>Yunnan Yukun</t>
   </si>
   <si>
+    <t>Inter Turku</t>
+  </si>
+  <si>
     <t>Turan Turkistan</t>
   </si>
   <si>
-    <t>Inter Turku</t>
-  </si>
-  <si>
     <t>Rosenborg</t>
   </si>
   <si>
@@ -325,15 +325,15 @@
     <t>Deportes Limache</t>
   </si>
   <si>
+    <t>HFX Wanderers FC</t>
+  </si>
+  <si>
+    <t>Pittsburgh Riverhounds</t>
+  </si>
+  <si>
     <t>Pacific FC</t>
   </si>
   <si>
-    <t>Pittsburgh Riverhounds</t>
-  </si>
-  <si>
-    <t>HFX Wanderers FC</t>
-  </si>
-  <si>
     <t>Indy Eleven</t>
   </si>
   <si>
@@ -349,10 +349,19 @@
     <t>Athletic Club</t>
   </si>
   <si>
+    <t>complete</t>
+  </si>
+  <si>
     <t>incomplete</t>
   </si>
   <si>
+    <t>['81']</t>
+  </si>
+  <si>
     <t>[]</t>
+  </si>
+  <si>
+    <t>['45+1', '71', '90+12']</t>
   </si>
 </sst>
 </file>
@@ -855,16 +864,16 @@
         <v>89</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="s">
         <v>111</v>
@@ -942,10 +951,10 @@
         <v>1.36</v>
       </c>
       <c r="AJ2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AK2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="AL2" s="3">
         <v>45856.22916666666</v>
@@ -983,16 +992,16 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L3">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="M3">
-        <v>3.79</v>
+        <v>4.1</v>
       </c>
       <c r="N3">
-        <v>3.87</v>
+        <v>3.93</v>
       </c>
       <c r="O3">
         <v>1.68</v>
@@ -1004,7 +1013,7 @@
         <v>2.12</v>
       </c>
       <c r="R3">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="S3">
         <v>4</v>
@@ -1013,13 +1022,13 @@
         <v>2.05</v>
       </c>
       <c r="U3">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="V3">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
       <c r="W3">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X3">
         <v>1</v>
@@ -1028,40 +1037,40 @@
         <v>12</v>
       </c>
       <c r="Z3">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AA3">
         <v>5.5</v>
       </c>
       <c r="AB3">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AC3">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="AD3">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AE3">
         <v>1.7</v>
       </c>
       <c r="AF3">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AG3">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AH3">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="AI3">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AJ3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AK3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AL3" s="3">
         <v>45856.27083333334</v>
@@ -1099,7 +1108,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L4">
         <v>2.67</v>
@@ -1174,10 +1183,10 @@
         <v>1.1</v>
       </c>
       <c r="AJ4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AK4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AL4" s="3">
         <v>45856.3125</v>
@@ -1215,7 +1224,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L5">
         <v>3.47</v>
@@ -1290,10 +1299,10 @@
         <v>1.18</v>
       </c>
       <c r="AJ5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AK5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AL5" s="3">
         <v>45856.3125</v>
@@ -1331,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L6">
         <v>2.01</v>
@@ -1406,10 +1415,10 @@
         <v>1.11</v>
       </c>
       <c r="AJ6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AK6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AL6" s="3">
         <v>45856.33333333334</v>
@@ -1447,16 +1456,16 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L7">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="M7">
-        <v>3.35</v>
+        <v>3.56</v>
       </c>
       <c r="N7">
-        <v>3.65</v>
+        <v>3.96</v>
       </c>
       <c r="O7">
         <v>1.44</v>
@@ -1468,64 +1477,64 @@
         <v>3</v>
       </c>
       <c r="R7">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S7">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="T7">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="U7">
         <v>1.37</v>
       </c>
       <c r="V7">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="W7">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X7">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>8.6</v>
+        <v>9.65</v>
       </c>
       <c r="Z7">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AA7">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AB7">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AC7">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AD7">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="AE7">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AF7">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG7">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AH7">
-        <v>6.5</v>
+        <v>6.15</v>
       </c>
       <c r="AI7">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AJ7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AK7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AL7" s="3">
         <v>45856.35416666666</v>
@@ -1563,7 +1572,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L8">
         <v>5.55</v>
@@ -1638,10 +1647,10 @@
         <v>1.16</v>
       </c>
       <c r="AJ8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AK8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AL8" s="3">
         <v>45856.35763888889</v>
@@ -1679,7 +1688,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L9">
         <v>1.85</v>
@@ -1754,10 +1763,10 @@
         <v>1.22</v>
       </c>
       <c r="AJ9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AK9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AL9" s="3">
         <v>45856.375</v>
@@ -1795,85 +1804,85 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L10">
-        <v>1.06</v>
+        <v>5.4</v>
       </c>
       <c r="M10">
-        <v>8.6</v>
+        <v>3.76</v>
       </c>
       <c r="N10">
-        <v>25</v>
+        <v>1.49</v>
       </c>
       <c r="O10">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="P10">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Q10">
-        <v>10</v>
+        <v>1.3</v>
       </c>
       <c r="R10">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S10">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="T10">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="U10">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="V10">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="W10">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X10">
         <v>1</v>
       </c>
       <c r="Y10">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Z10">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AA10">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AB10">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AC10">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AD10">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AE10">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AF10">
-        <v>3.3</v>
+        <v>1.77</v>
       </c>
       <c r="AG10">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="AH10">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AI10">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AJ10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AK10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AL10" s="3">
         <v>45856.5</v>
@@ -1911,43 +1920,43 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L11">
-        <v>8</v>
+        <v>1.05</v>
       </c>
       <c r="M11">
-        <v>5.05</v>
+        <v>10</v>
       </c>
       <c r="N11">
-        <v>1.33</v>
+        <v>23</v>
       </c>
       <c r="O11">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="P11">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Q11">
-        <v>1.3</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S11">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="T11">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="U11">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="V11">
-        <v>4.3</v>
+        <v>4.65</v>
       </c>
       <c r="W11">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X11">
         <v>1</v>
@@ -1956,40 +1965,40 @@
         <v>19</v>
       </c>
       <c r="Z11">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AA11">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AB11">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AC11">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="AD11">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AE11">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AF11">
-        <v>1.72</v>
+        <v>3.6</v>
       </c>
       <c r="AG11">
-        <v>2.02</v>
+        <v>1.21</v>
       </c>
       <c r="AH11">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="AI11">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AJ11" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AK11" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AL11" s="3">
         <v>45856.5</v>
@@ -2027,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L12">
         <v>2.45</v>
@@ -2102,10 +2111,10 @@
         <v>1.2</v>
       </c>
       <c r="AJ12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AK12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AL12" s="3">
         <v>45856.54166666666</v>
@@ -2143,16 +2152,16 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L13">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="M13">
-        <v>3.27</v>
+        <v>3.06</v>
       </c>
       <c r="N13">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="O13">
         <v>1.6</v>
@@ -2164,64 +2173,64 @@
         <v>2.95</v>
       </c>
       <c r="R13">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="S13">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="T13">
         <v>3.3</v>
       </c>
       <c r="U13">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="V13">
         <v>9</v>
       </c>
       <c r="W13">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X13">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y13">
-        <v>7.02</v>
+        <v>6</v>
       </c>
       <c r="Z13">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AA13">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AB13">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AC13">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AD13">
-        <v>5.03</v>
+        <v>4.7</v>
       </c>
       <c r="AE13">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF13">
         <v>2.2</v>
       </c>
       <c r="AG13">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AH13">
         <v>9.5</v>
       </c>
       <c r="AI13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AJ13" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AK13" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AL13" s="3">
         <v>45856.79166666666</v>
@@ -2259,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L14">
         <v>1.53</v>
@@ -2334,10 +2343,10 @@
         <v>1.06</v>
       </c>
       <c r="AJ14" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AK14" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AL14" s="3">
         <v>45856.8125</v>
@@ -2375,7 +2384,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L15">
         <v>2.15</v>
@@ -2450,10 +2459,10 @@
         <v>1.09</v>
       </c>
       <c r="AJ15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AK15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AL15" s="3">
         <v>45856.83333333334</v>
@@ -2491,85 +2500,85 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L16">
-        <v>1.59</v>
+        <v>1.9</v>
       </c>
       <c r="M16">
-        <v>3.84</v>
+        <v>3.3</v>
       </c>
       <c r="N16">
-        <v>5.06</v>
+        <v>3.7</v>
       </c>
       <c r="O16">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="P16">
-        <v>10</v>
+        <v>8.75</v>
       </c>
       <c r="Q16">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="R16">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="S16">
-        <v>2.99</v>
+        <v>2.65</v>
       </c>
       <c r="T16">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U16">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="V16">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W16">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X16">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z16">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AA16">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AB16">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AC16">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AD16">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="AE16">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AF16">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG16">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH16">
-        <v>5.25</v>
+        <v>6.4</v>
       </c>
       <c r="AI16">
         <v>1.08</v>
       </c>
       <c r="AJ16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AK16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AL16" s="3">
         <v>45856.83333333334</v>
@@ -2607,13 +2616,13 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L17">
-        <v>2.91</v>
+        <v>2.81</v>
       </c>
       <c r="M17">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="N17">
         <v>2.43</v>
@@ -2643,34 +2652,34 @@
         <v>11</v>
       </c>
       <c r="W17">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X17">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
         <v>6</v>
       </c>
       <c r="Z17">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AA17">
-        <v>2.51</v>
+        <v>2.44</v>
       </c>
       <c r="AB17">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AC17">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AD17">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="AE17">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF17">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AG17">
         <v>1.75</v>
@@ -2682,10 +2691,10 @@
         <v>1.04</v>
       </c>
       <c r="AJ17" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AK17" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AL17" s="3">
         <v>45856.83333333334</v>
@@ -2723,85 +2732,85 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L18">
-        <v>2.26</v>
+        <v>1.6</v>
       </c>
       <c r="M18">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="N18">
-        <v>2.87</v>
+        <v>4.9</v>
       </c>
       <c r="O18">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="P18">
-        <v>8.75</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="R18">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S18">
-        <v>2.65</v>
+        <v>2.92</v>
       </c>
       <c r="T18">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="U18">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V18">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="W18">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X18">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y18">
-        <v>8.75</v>
+        <v>11</v>
       </c>
       <c r="Z18">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AA18">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="AB18">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AC18">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AD18">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="AE18">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AF18">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG18">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AH18">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="AI18">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AJ18" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AK18" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AL18" s="3">
         <v>45856.83333333334</v>
@@ -2839,16 +2848,16 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L19">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="M19">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="N19">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="O19">
         <v>1.7</v>
@@ -2860,10 +2869,10 @@
         <v>2.29</v>
       </c>
       <c r="R19">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S19">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="T19">
         <v>2.8</v>
@@ -2878,22 +2887,22 @@
         <v>1.08</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y19">
         <v>8.800000000000001</v>
       </c>
       <c r="Z19">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AA19">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="AB19">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AC19">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AD19">
         <v>3.4</v>
@@ -2902,22 +2911,22 @@
         <v>1.3</v>
       </c>
       <c r="AF19">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AG19">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AH19">
         <v>6.5</v>
       </c>
       <c r="AI19">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AJ19" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AK19" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AL19" s="3">
         <v>45856.85416666666</v>
@@ -2955,7 +2964,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L20">
         <v>1.6</v>
@@ -2976,64 +2985,64 @@
         <v>3</v>
       </c>
       <c r="R20">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="S20">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T20">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="U20">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="V20">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="W20">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y20">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z20">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AA20">
-        <v>4.45</v>
+        <v>4.75</v>
       </c>
       <c r="AB20">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AC20">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AD20">
-        <v>2.17</v>
+        <v>2.35</v>
       </c>
       <c r="AE20">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AF20">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AG20">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AH20">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="AI20">
         <v>1.22</v>
       </c>
       <c r="AJ20" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AK20" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AL20" s="3">
         <v>45856.875</v>
@@ -3071,7 +3080,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L21">
         <v>2</v>
@@ -3146,10 +3155,10 @@
         <v>1.05</v>
       </c>
       <c r="AJ21" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AK21" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AL21" s="3">
         <v>45856.89583333334</v>
@@ -3187,16 +3196,16 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L22">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="M22">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="N22">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="O22">
         <v>2.88</v>
@@ -3214,16 +3223,16 @@
         <v>3.8</v>
       </c>
       <c r="T22">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="U22">
         <v>1.61</v>
       </c>
       <c r="V22">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="W22">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X22">
         <v>0</v>
@@ -3238,34 +3247,34 @@
         <v>4.7</v>
       </c>
       <c r="AB22">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AC22">
         <v>2.75</v>
       </c>
       <c r="AD22">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AE22">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AF22">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AG22">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AH22">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AI22">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AJ22" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AK22" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AL22" s="3">
         <v>45856.89583333334</v>
@@ -3303,16 +3312,16 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L23">
-        <v>2.29</v>
+        <v>1.79</v>
       </c>
       <c r="M23">
-        <v>3.05</v>
+        <v>3.23</v>
       </c>
       <c r="N23">
-        <v>2.98</v>
+        <v>3.97</v>
       </c>
       <c r="O23">
         <v>1.83</v>
@@ -3327,25 +3336,25 @@
         <v>1.5</v>
       </c>
       <c r="S23">
-        <v>2.47</v>
+        <v>2.35</v>
       </c>
       <c r="T23">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="U23">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V23">
-        <v>9.9</v>
+        <v>11</v>
       </c>
       <c r="W23">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X23">
         <v>1.1</v>
       </c>
       <c r="Y23">
-        <v>6.84</v>
+        <v>6.5</v>
       </c>
       <c r="Z23">
         <v>1.5</v>
@@ -3354,34 +3363,34 @@
         <v>2.47</v>
       </c>
       <c r="AB23">
-        <v>2.47</v>
+        <v>2.2</v>
       </c>
       <c r="AC23">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AD23">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AE23">
         <v>1.17</v>
       </c>
       <c r="AF23">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AG23">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AH23">
         <v>9</v>
       </c>
       <c r="AI23">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AJ23" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AK23" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AL23" s="3">
         <v>45856.89583333334</v>

--- a/jogos_2025-07-18.xlsx
+++ b/jogos_2025-07-18.xlsx
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,19 +1675,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1697,17 +1697,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['52']</t>
         </is>
       </c>
       <c r="AG10" t="n">
@@ -1794,119 +1794,119 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O11" t="n">
+        <v>7</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V11" t="n">
         <v>1</v>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['28', '33']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['52']</t>
+          <t>['7', '31']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45856.5</v>
@@ -1923,119 +1923,119 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>8.5</v>
+        <v>1.64</v>
       </c>
       <c r="M12" t="n">
-        <v>5.5</v>
+        <v>3.74</v>
       </c>
       <c r="N12" t="n">
-        <v>1.28</v>
+        <v>5.65</v>
       </c>
       <c r="O12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.37</v>
+        <v>2.15</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.85</v>
+        <v>1.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['28', '33']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['7', '31']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45856.5</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,25 +2191,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.06</v>
+        <v>1.53</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>4.39</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>5.28</v>
       </c>
       <c r="O14" t="n">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.33</v>
+        <v>4.45</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA14" t="n">
         <v>2.6</v>
       </c>
-      <c r="T14" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U14" t="n">
+      <c r="AB14" t="n">
         <v>1.33</v>
       </c>
-      <c r="V14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AC14" t="n">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['81']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['17', '42', '45', '75']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.71</v>
+        <v>2.3</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.85</v>
+        <v>1.45</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.35</v>
+        <v>2.96</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45856.54166666666</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="M15" t="n">
-        <v>4.39</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>5.28</v>
+        <v>3.6</v>
       </c>
       <c r="O15" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="P15" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.45</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>3.22</v>
+        <v>2.85</v>
       </c>
       <c r="T15" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="U15" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W15" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="X15" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.6</v>
+        <v>2.92</v>
       </c>
       <c r="AB15" t="n">
         <v>1.33</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['17', '42', '45', '75']</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.45</v>
+        <v>1.77</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.96</v>
+        <v>2.4</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45856.54166666666</v>
@@ -2439,35 +2439,35 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Slavia Praha II</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" t="n">
         <v>1</v>
       </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['20', '87']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['65']</t>
+          <t>['5', '34']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45856.54166666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,109 +2578,109 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['13']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['90+4']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45856.54166666666</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,25 +2707,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
+          <t>['81']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>['23', '81']</t>
-        </is>
-      </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45856.54166666666</v>
@@ -2836,25 +2836,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Slavia Praha II</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2920,12 +2920,12 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['44', '66']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['45+1']</t>
+          <t>['65']</t>
         </is>
       </c>
       <c r="AG19" t="n">
@@ -2955,35 +2955,35 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['20', '87']</t>
+          <t>['44', '66']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['5', '34']</t>
+          <t>['45+1']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45856.54166666666</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,77 +3120,77 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>8.19</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['3', '40']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['58', '77']</t>
+          <t>['23', '81']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,19 +3868,19 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27" t="n">
         <v>1</v>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.85</v>
+        <v>1.8</v>
       </c>
       <c r="M27" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="N27" t="n">
-        <v>1.95</v>
+        <v>3.65</v>
       </c>
       <c r="O27" t="n">
-        <v>4.9</v>
+        <v>2.2</v>
       </c>
       <c r="P27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X27" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD27" t="n">
         <v>2</v>
       </c>
-      <c r="Q27" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X27" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['32']</t>
+          <t>['19']</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['19']</t>
+          <t>['45+3', '90']</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.8</v>
+        <v>1.23</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.17</v>
+        <v>1.89</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.67</v>
+        <v>2.75</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45856.63541666666</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,19 +3997,19 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G28" t="n">
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O28" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>['32']</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>['19']</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
         <v>1.8</v>
       </c>
-      <c r="M28" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N28" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T28" t="n">
+      <c r="AH28" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI28" t="n">
         <v>2.5</v>
       </c>
-      <c r="U28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X28" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>['19']</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>['45+3', '90']</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AJ28" t="n">
-        <v>2.75</v>
+        <v>1.67</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45856.63541666666</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,25 +4255,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G30" t="n">
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N30" t="n">
-        <v>4.1</v>
+        <v>4.75</v>
       </c>
       <c r="O30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P30" t="n">
         <v>2.25</v>
       </c>
-      <c r="P30" t="n">
-        <v>2.24</v>
-      </c>
       <c r="Q30" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="R30" t="n">
         <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="T30" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="U30" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V30" t="n">
         <v>1.04</v>
       </c>
       <c r="W30" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X30" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['11']</t>
+          <t>['45+1']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['26', '2', '52', '60']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45856.64583333334</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,25 +4384,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G31" t="n">
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>4.75</v>
+        <v>4.1</v>
       </c>
       <c r="O31" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="P31" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="R31" t="n">
         <v>1.3</v>
       </c>
       <c r="S31" t="n">
-        <v>3.3</v>
+        <v>2.65</v>
       </c>
       <c r="T31" t="n">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="U31" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V31" t="n">
         <v>1.04</v>
       </c>
       <c r="W31" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X31" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['45+1']</t>
+          <t>['11']</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>['26', '2', '52', '60']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45856.64583333334</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4786,7 +4786,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4797,65 +4797,65 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="N34" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="O34" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="P34" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="R34" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S34" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="T34" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U34" t="n">
         <v>1.4</v>
       </c>
       <c r="V34" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W34" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="X34" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['10', '47']</t>
+          <t>['78', '80']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -4864,16 +4864,16 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45856.83333333334</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,16 +4900,16 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -4926,65 +4926,65 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.6</v>
+        <v>2.81</v>
       </c>
       <c r="M35" t="n">
-        <v>3.65</v>
+        <v>3.01</v>
       </c>
       <c r="N35" t="n">
-        <v>4.9</v>
+        <v>2.43</v>
       </c>
       <c r="O35" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="P35" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="Q35" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="R35" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="T35" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="U35" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="V35" t="n">
         <v>1.04</v>
       </c>
       <c r="W35" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="X35" t="n">
-        <v>3.7</v>
+        <v>2.44</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.8</v>
+        <v>2.37</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.83</v>
+        <v>1.48</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.88</v>
+        <v>4.9</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.37</v>
+        <v>1.14</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>['78', '80']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
@@ -4993,16 +4993,16 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.4</v>
+        <v>1.99</v>
       </c>
       <c r="AJ35" t="n">
-        <v>3.5</v>
+        <v>2.16</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45856.83333333334</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,22 +5029,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.81</v>
+        <v>1.9</v>
       </c>
       <c r="M36" t="n">
-        <v>3.01</v>
+        <v>3.3</v>
       </c>
       <c r="N36" t="n">
-        <v>2.43</v>
+        <v>3.7</v>
       </c>
       <c r="O36" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="P36" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R36" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="S36" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="T36" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="U36" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="V36" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W36" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="X36" t="n">
-        <v>2.44</v>
+        <v>3.25</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.37</v>
+        <v>1.73</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.48</v>
+        <v>1.91</v>
       </c>
       <c r="AA36" t="n">
-        <v>4.9</v>
+        <v>2.59</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
+          <t>['10', '47']</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG36" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.99</v>
+        <v>1.57</v>
       </c>
       <c r="AJ36" t="n">
-        <v>2.16</v>
+        <v>2.6</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45856.83333333334</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5431,7 +5431,7 @@
         <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="M39" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N39" t="n">
         <v>4.75</v>
       </c>
       <c r="O39" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X39" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z39" t="n">
         <v>2.3</v>
       </c>
-      <c r="P39" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>5</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X39" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AA39" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>['14', '42']</t>
+          <t>['56', '81']</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>['59']</t>
+          <t>['84']</t>
         </is>
       </c>
       <c r="AG39" t="n">
         <v>1.17</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.98</v>
+        <v>2.9</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AJ39" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45856.875</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5560,7 +5560,7 @@
         <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -5571,83 +5571,83 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="M40" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N40" t="n">
         <v>4.75</v>
       </c>
       <c r="O40" t="n">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="P40" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="Q40" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="R40" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="S40" t="n">
-        <v>3.28</v>
+        <v>2.75</v>
       </c>
       <c r="T40" t="n">
-        <v>2.18</v>
+        <v>2.75</v>
       </c>
       <c r="U40" t="n">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="V40" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="W40" t="n">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="X40" t="n">
-        <v>5.25</v>
+        <v>3.3</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AD40" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>['56', '81']</t>
+          <t>['14', '42']</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>['84']</t>
+          <t>['59']</t>
         </is>
       </c>
       <c r="AG40" t="n">
         <v>1.17</v>
       </c>
       <c r="AH40" t="n">
-        <v>2.9</v>
+        <v>1.98</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AJ40" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45856.875</v>
